--- a/SEO_Palabras_Clave_Limpias.xlsx
+++ b/SEO_Palabras_Clave_Limpias.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F243"/>
+  <dimension ref="A1:F290"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -532,7 +532,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>antojos hamburguesas de arrachera en ixtepec</t>
+          <t>abierto hoy en ixtepec</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -562,7 +562,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>comida rapida alitas bbq en la noche en ixtepec</t>
+          <t>antojos hamburguesas de arrachera en ixtepec</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>comida rapida alitas picosas en ixtepec</t>
+          <t>boneless en el istmo</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>comida rapida boneless a domicilio en ixtepec</t>
+          <t>boneless en ixtepec</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -652,7 +652,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>comida rapida frappes en ciudad ixtepec</t>
+          <t>comida rapida alitas en ciudad ixtepec</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>comida rapida hamburguesas de arrachera a domicilio en ixtepec</t>
+          <t>comida rapida alitas picosas en ixtepec</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>comida rapida hamburguesas de arrachera en ciudad ixtepec</t>
+          <t>comida rapida boneless a domicilio en ixtepec</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>cono de boneless istmo</t>
+          <t>comida rapida frappes en ciudad ixtepec</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>cono de boneless ixtepec</t>
+          <t>comida rapida hamburguesas de arrachera a domicilio en ixtepec</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -802,7 +802,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>donde cenar tarde en ixtepec</t>
+          <t>comida rapida hamburguesas de arrachera en ciudad ixtepec</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -817,7 +817,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Busqueda</t>
+          <t>Informativa</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>donde comer alitas bbq cerca del parque ixtepec</t>
+          <t>cono de boneless en el istmo</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Busqueda</t>
+          <t>Informativa</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>donde comer alitas picosas a domicilio en ixtepec</t>
+          <t>cono de boneless en ixtepec</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Busqueda</t>
+          <t>Informativa</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>donde comer boneless en ciudad ixtepec</t>
+          <t>cono de boneless istmo</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Busqueda</t>
+          <t>Informativa</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>donde comer comida para llevar en el istmo</t>
+          <t>cono de boneless ixtepec</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Busqueda</t>
+          <t>Informativa</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>donde comer con ninos en ixtepec</t>
+          <t>donde cenar conos de boneless en el istmo de tehuantepec</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>donde comer hamburguesas en ciudad ixtepec</t>
+          <t>donde cenar hoy en ixtepec</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>donde comprar hamburguesas de arrachera en ixtepec</t>
+          <t>donde cenar tarde en ixtepec</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>donde queda mr papas en ixtepec</t>
+          <t>donde comer alitas en ciudad ixtepec</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Marca</t>
+          <t>Busqueda</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>donde salir a comer alitas bbq en ixtepec</t>
+          <t>donde comer alitas picosas a domicilio en ixtepec</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>donde salir a comer frappes frios a domicilio en ixtepec</t>
+          <t>donde comer boneless en ciudad ixtepec</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>donde salir a comer hamburguesas de arrachera en ciudad ixtepec</t>
+          <t>donde comer cerca de mi en ixtepec</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>hamburguesas a domicilio en ixtepec</t>
+          <t>donde comer con ninos en ixtepec</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Informativa</t>
+          <t>Busqueda</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>horario de mr papas ixtepec</t>
+          <t>donde comer hamburguesas en ciudad ixtepec</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Marca</t>
+          <t>Busqueda</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>mejores lugares para comer alitas picosas en ixtepec</t>
+          <t>donde comer hoy en el istmo</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Comparativa</t>
+          <t>Busqueda</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>mejores lugares para comer comida para llevar a domicilio en ixtepec</t>
+          <t>donde comer hoy en ixtepec</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Comparativa</t>
+          <t>Busqueda</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -1282,7 +1282,7 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>mejores lugares para comer hamburguesas de arrachera cerca del parque ixtepec</t>
+          <t>donde queda mr papas en ixtepec</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Comparativa</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>menu de mr papas ixtepec</t>
+          <t>donde salir a comer alitas bbq en ixtepec</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Marca</t>
+          <t>Busqueda</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>precios de mr papas ixtepec</t>
+          <t>donde salir a comer conos de boneless en el istmo</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Marca</t>
+          <t>Busqueda</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>promociones de frappes frios en ixtepec</t>
+          <t>donde salir a comer frappes frios a domicilio en ixtepec</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Transaccional</t>
+          <t>Busqueda</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>promociones de hamburguesas de arrachera cerca del parque ixtepec</t>
+          <t>donde salir a comer hamburguesas de arrachera en ciudad ixtepec</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Transaccional</t>
+          <t>Busqueda</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>promociones de hamburguesas de arrachera en el istmo de tehuantepec</t>
+          <t>donde venden hamburguesas en ixtepec</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Transaccional</t>
+          <t>Busqueda</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>promociones de hamburguesas en el istmo</t>
+          <t>frappes cerca de mi en ixtepec</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Transaccional</t>
+          <t>Informativa</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
@@ -1492,7 +1492,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>restaurantes abiertos hoy en ixtepec</t>
+          <t>frappes en ixtepec</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>restaurantes de comida para llevar en ixtepec</t>
+          <t>hamburguesas a domicilio en ixtepec</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>restaurantes para familias en el istmo</t>
+          <t>hamburguesas cerca de mi en ixtepec</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -1582,17 +1582,17 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>alitas a domicilio en ixtepec</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>MEDIO-ALTO</t>
+          <t>hamburguesas en el istmo</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>ALTO</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>50-100</t>
+          <t>100-500+</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>Buen volumen moderado</t>
+          <t>Palabra clave principal</t>
         </is>
       </c>
     </row>
@@ -1612,17 +1612,17 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>antojos nocturnos en ixtepec</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>MEDIO-ALTO</t>
+          <t>hamburguesas en ixtepec</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>ALTO</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>50-100</t>
+          <t>100-500+</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>Buen volumen moderado</t>
+          <t>Palabra clave principal</t>
         </is>
       </c>
     </row>
@@ -1642,27 +1642,27 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>bebidas frias en el istmo</t>
-        </is>
-      </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>MEDIO-ALTO</t>
+          <t>horario de mr papas ixtepec</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>ALTO</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>50-100</t>
+          <t>100-500+</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Informativa</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>Buen volumen moderado</t>
+          <t>Palabra clave principal</t>
         </is>
       </c>
     </row>
@@ -1672,27 +1672,27 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>boneless por kilo en el istmo</t>
-        </is>
-      </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>MEDIO-ALTO</t>
+          <t>las mejores hamburguesas en el istmo</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>ALTO</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>50-100</t>
+          <t>100-500+</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Informativa</t>
+          <t>Comparativa</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>Buen volumen moderado</t>
+          <t>Palabra clave principal</t>
         </is>
       </c>
     </row>
@@ -1702,27 +1702,27 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>cenar rico y barato en ixtepec</t>
-        </is>
-      </c>
-      <c r="C41" s="5" t="inlineStr">
-        <is>
-          <t>MEDIO-ALTO</t>
+          <t>las mejores hamburguesas en ixtepec</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>ALTO</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>50-100</t>
+          <t>100-500+</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Informativa</t>
+          <t>Comparativa</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>Buen volumen moderado</t>
+          <t>Palabra clave principal</t>
         </is>
       </c>
     </row>
@@ -1732,27 +1732,27 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>comida nocturna istmo</t>
-        </is>
-      </c>
-      <c r="C42" s="5" t="inlineStr">
-        <is>
-          <t>MEDIO-ALTO</t>
+          <t>mejor restaurante de comida rapida en el istmo</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>ALTO</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>50-100</t>
+          <t>100-500+</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Informativa</t>
+          <t>Comparativa</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>Buen volumen moderado</t>
+          <t>Palabra clave principal</t>
         </is>
       </c>
     </row>
@@ -1762,27 +1762,27 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>comida para fiestas en ixtepec</t>
-        </is>
-      </c>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t>MEDIO-ALTO</t>
+          <t>mejor restaurante de comida rapida en ixtepec</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>ALTO</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>50-100</t>
+          <t>100-500+</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Informativa</t>
+          <t>Comparativa</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>Buen volumen moderado</t>
+          <t>Palabra clave principal</t>
         </is>
       </c>
     </row>
@@ -1792,27 +1792,27 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>comida rapida abierta de noche en ixtepec</t>
-        </is>
-      </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>MEDIO-ALTO</t>
+          <t>mejores lugares para comer comida para llevar a domicilio en ixtepec</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>ALTO</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>50-100</t>
+          <t>100-500+</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Informativa</t>
+          <t>Comparativa</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>Buen volumen moderado</t>
+          <t>Palabra clave principal</t>
         </is>
       </c>
     </row>
@@ -1822,27 +1822,27 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>comida rapida alitas en ciudad ixtepec</t>
-        </is>
-      </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>MEDIO-ALTO</t>
+          <t>mejores lugares para comer frappes en el istmo de tehuantepec</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>ALTO</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>50-100</t>
+          <t>100-500+</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Informativa</t>
+          <t>Comparativa</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>Buen volumen moderado</t>
+          <t>Palabra clave principal</t>
         </is>
       </c>
     </row>
@@ -1852,27 +1852,27 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>comida rapida alitas picosas en ciudad ixtepec</t>
-        </is>
-      </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>MEDIO-ALTO</t>
+          <t>mejores lugares para comer hamburguesas de arrachera cerca del parque ixtepec</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>ALTO</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>50-100</t>
+          <t>100-500+</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Informativa</t>
+          <t>Comparativa</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>Buen volumen moderado</t>
+          <t>Palabra clave principal</t>
         </is>
       </c>
     </row>
@@ -1882,27 +1882,27 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>comida rapida alitas picosas en la noche en ixtepec</t>
-        </is>
-      </c>
-      <c r="C47" s="5" t="inlineStr">
-        <is>
-          <t>MEDIO-ALTO</t>
+          <t>menu de mr papas ixtepec</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>ALTO</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>50-100</t>
+          <t>100-500+</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Informativa</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>Buen volumen moderado</t>
+          <t>Palabra clave principal</t>
         </is>
       </c>
     </row>
@@ -1912,27 +1912,27 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>comida rapida boneless de madrugada en el istmo</t>
-        </is>
-      </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>MEDIO-ALTO</t>
+          <t>precios de mr papas ixtepec</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>ALTO</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>50-100</t>
+          <t>100-500+</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Informativa</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>Buen volumen moderado</t>
+          <t>Palabra clave principal</t>
         </is>
       </c>
     </row>
@@ -1942,27 +1942,27 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>comida rapida comida para llevar en el istmo de tehuantepec</t>
-        </is>
-      </c>
-      <c r="C49" s="5" t="inlineStr">
-        <is>
-          <t>MEDIO-ALTO</t>
+          <t>promociones de hamburguesas de arrachera en el istmo de tehuantepec</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>ALTO</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>50-100</t>
+          <t>100-500+</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Informativa</t>
+          <t>Transaccional</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>Buen volumen moderado</t>
+          <t>Palabra clave principal</t>
         </is>
       </c>
     </row>
@@ -1972,27 +1972,27 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>comida rapida economica en ixtepec</t>
-        </is>
-      </c>
-      <c r="C50" s="5" t="inlineStr">
-        <is>
-          <t>MEDIO-ALTO</t>
+          <t>promociones de hamburguesas en el istmo</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>ALTO</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>50-100</t>
+          <t>100-500+</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Informativa</t>
+          <t>Transaccional</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>Buen volumen moderado</t>
+          <t>Palabra clave principal</t>
         </is>
       </c>
     </row>
@@ -2002,17 +2002,17 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>comida rapida frappes de madrugada en el istmo</t>
-        </is>
-      </c>
-      <c r="C51" s="5" t="inlineStr">
-        <is>
-          <t>MEDIO-ALTO</t>
+          <t>restaurantes abiertos hoy en ixtepec</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>ALTO</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>50-100</t>
+          <t>100-500+</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>Buen volumen moderado</t>
+          <t>Palabra clave principal</t>
         </is>
       </c>
     </row>
@@ -2032,17 +2032,17 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>comida rapida frappes frios en la noche en ixtepec</t>
-        </is>
-      </c>
-      <c r="C52" s="5" t="inlineStr">
-        <is>
-          <t>MEDIO-ALTO</t>
+          <t>restaurantes de alitas en ixtepec</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>ALTO</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>50-100</t>
+          <t>100-500+</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>Buen volumen moderado</t>
+          <t>Palabra clave principal</t>
         </is>
       </c>
     </row>
@@ -2062,17 +2062,17 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>comida rapida papas a la francesa para bajar la cruda en el istmo</t>
-        </is>
-      </c>
-      <c r="C53" s="5" t="inlineStr">
-        <is>
-          <t>MEDIO-ALTO</t>
+          <t>restaurantes de frappes en el istmo de tehuantepec</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>ALTO</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>50-100</t>
+          <t>100-500+</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>Buen volumen moderado</t>
+          <t>Palabra clave principal</t>
         </is>
       </c>
     </row>
@@ -2092,27 +2092,27 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>donde cenar alitas picosas en la noche en ixtepec</t>
-        </is>
-      </c>
-      <c r="C54" s="5" t="inlineStr">
-        <is>
-          <t>MEDIO-ALTO</t>
+          <t>restaurantes para familias en el istmo</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>ALTO</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>50-100</t>
+          <t>100-500+</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Busqueda</t>
+          <t>Informativa</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>Buen volumen moderado</t>
+          <t>Palabra clave principal</t>
         </is>
       </c>
     </row>
@@ -2122,7 +2122,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>donde cenar boneless de madrugada en el istmo</t>
+          <t>alitas bbq en el istmo</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Busqueda</t>
+          <t>Informativa</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>donde cenar conos de boneless en el istmo de tehuantepec</t>
+          <t>alitas bbq en ixtepec</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Busqueda</t>
+          <t>Informativa</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>donde comer alitas en ciudad ixtepec</t>
+          <t>alitas cerca de mi en ixtepec</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
@@ -2197,7 +2197,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Busqueda</t>
+          <t>Informativa</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>donde comer frappes frios en el istmo de tehuantepec</t>
+          <t>alitas en el istmo</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Busqueda</t>
+          <t>Informativa</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
@@ -2242,7 +2242,7 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>donde comer hoy en ixtepec</t>
+          <t>alitas en ixtepec</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Busqueda</t>
+          <t>Informativa</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>donde comprar comida para llevar a domicilio en ixtepec</t>
+          <t>alitas picosas en ixtepec</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Busqueda</t>
+          <t>Informativa</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>donde comprar frappes a domicilio en ixtepec</t>
+          <t>antojos nocturnos en ixtepec</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Busqueda</t>
+          <t>Informativa</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
@@ -2332,7 +2332,7 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>donde comprar frappes en el istmo</t>
+          <t>combo familiar de alitas en el istmo</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Busqueda</t>
+          <t>Informativa</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>donde comprar hamburguesas de arrachera de madrugada en el istmo</t>
+          <t>comida nocturna istmo</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Busqueda</t>
+          <t>Informativa</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>donde pedir conos de boneless a domicilio en ixtepec</t>
+          <t>comida rapida alitas bbq en la noche en ixtepec</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
@@ -2407,7 +2407,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Busqueda</t>
+          <t>Informativa</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>donde pedir frappes a domicilio en ixtepec</t>
+          <t>comida rapida alitas picosas en ciudad ixtepec</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Busqueda</t>
+          <t>Informativa</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>donde pedir frappes en el istmo</t>
+          <t>comida rapida alitas picosas en la noche en ixtepec</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Busqueda</t>
+          <t>Informativa</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>donde pedir frappes en ixtepec</t>
+          <t>comida rapida boneless de madrugada en el istmo</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Busqueda</t>
+          <t>Informativa</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>donde pedir frappes frios a domicilio en ixtepec</t>
+          <t>comida rapida comida para llevar en el istmo de tehuantepec</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Busqueda</t>
+          <t>Informativa</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>donde salir a comer comida para llevar cerca del parque ixtepec</t>
+          <t>comida rapida economica en ixtepec</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Busqueda</t>
+          <t>Informativa</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>donde salir a comer comida para llevar de madrugada en el istmo</t>
+          <t>comida rapida en ixtepec hoy</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Busqueda</t>
+          <t>Informativa</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>donde salir a comer conos de boneless en el istmo</t>
+          <t>comida rapida frappes de madrugada en el istmo</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Busqueda</t>
+          <t>Informativa</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>donde salir a comer en el istmo</t>
+          <t>comida rapida frappes frios en la noche en ixtepec</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Busqueda</t>
+          <t>Informativa</t>
         </is>
       </c>
       <c r="F72" s="3" t="inlineStr">
@@ -2662,7 +2662,7 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>donde salir a comer hamburguesas de madrugada en el istmo</t>
+          <t>donde cenar alitas picosas en la noche en ixtepec</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>donde salir a comer papas a la francesa en el istmo de tehuantepec</t>
+          <t>donde cenar boneless de madrugada en el istmo</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>donde venden alitas picosas a domicilio en ixtepec</t>
+          <t>donde comer alitas bbq cerca del parque ixtepec</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>donde venden frappes en el istmo</t>
+          <t>donde comer comida para llevar en el istmo</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
@@ -2782,7 +2782,7 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>donde venden hamburguesas en ixtepec</t>
+          <t>donde comer frappes frios en el istmo de tehuantepec</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>frappes cerca de mi en ixtepec</t>
+          <t>donde comprar frappes a domicilio en ixtepec</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Informativa</t>
+          <t>Busqueda</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>hamburguesa de arrachera a domicilio ixtepec</t>
+          <t>donde comprar frappes en el istmo</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Informativa</t>
+          <t>Busqueda</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
@@ -2872,7 +2872,7 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>hamburguesas gigantes y jugosas en el istmo</t>
+          <t>donde comprar hamburguesas de arrachera en ixtepec</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Informativa</t>
+          <t>Busqueda</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr">
@@ -2902,7 +2902,7 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>las mejores boneless a domicilio en ixtepec</t>
+          <t>donde pedir frappes a domicilio en ixtepec</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Comparativa</t>
+          <t>Busqueda</t>
         </is>
       </c>
       <c r="F81" s="3" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>las mejores hamburguesas en el istmo</t>
+          <t>donde pedir frappes en el istmo</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
@@ -2947,7 +2947,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Comparativa</t>
+          <t>Busqueda</t>
         </is>
       </c>
       <c r="F82" s="3" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>las mejores hamburguesas en ixtepec</t>
+          <t>donde pedir frappes en ixtepec</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Comparativa</t>
+          <t>Busqueda</t>
         </is>
       </c>
       <c r="F83" s="3" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>las mejores hamburguesas en la noche en ixtepec</t>
+          <t>donde pedir frappes frios a domicilio en ixtepec</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
@@ -3007,7 +3007,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Comparativa</t>
+          <t>Busqueda</t>
         </is>
       </c>
       <c r="F84" s="3" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>las mejores papas a la francesa a domicilio en ixtepec</t>
+          <t>donde salir a comer hamburguesas de madrugada en el istmo</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Comparativa</t>
+          <t>Busqueda</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr">
@@ -3052,7 +3052,7 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>lugares para cenar boneless a domicilio en ixtepec</t>
+          <t>donde salir a comer papas a la francesa en el istmo de tehuantepec</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Informativa</t>
+          <t>Busqueda</t>
         </is>
       </c>
       <c r="F86" s="3" t="inlineStr">
@@ -3082,7 +3082,7 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>lugares para cenar hamburguesas de arrachera en el istmo</t>
+          <t>donde venden alitas picosas a domicilio en ixtepec</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Informativa</t>
+          <t>Busqueda</t>
         </is>
       </c>
       <c r="F87" s="3" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>lugares para cenar hamburguesas de arrachera en el istmo de tehuantepec</t>
+          <t>donde venden boneless en la noche en ixtepec</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Informativa</t>
+          <t>Busqueda</t>
         </is>
       </c>
       <c r="F88" s="3" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>lugares para visitar en ixtepec</t>
+          <t>donde venden frappes en el istmo</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Informativa</t>
+          <t>Busqueda</t>
         </is>
       </c>
       <c r="F89" s="3" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>mejores lugares para comer alitas bbq para bajar la cruda en el istmo</t>
+          <t>el mejor restaurante de ixtepec</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>mejores lugares para comer alitas picosas cerca del parque ixtepec</t>
+          <t>el mejor restaurante del istmo</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
@@ -3232,7 +3232,7 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>mejores lugares para comer botanas a domicilio en ixtepec</t>
+          <t>frappe de capuchino istmo</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Comparativa</t>
+          <t>Informativa</t>
         </is>
       </c>
       <c r="F92" s="3" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>mejores lugares para comer comida para llevar cerca del parque ixtepec</t>
+          <t>frappe de mazapan ixtepec</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
@@ -3277,7 +3277,7 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Comparativa</t>
+          <t>Informativa</t>
         </is>
       </c>
       <c r="F93" s="3" t="inlineStr">
@@ -3292,7 +3292,7 @@
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>mejores lugares para comer frappes en el istmo de tehuantepec</t>
+          <t>las mejores boneless a domicilio en ixtepec</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>mejores lugares para comer frappes frios en el istmo</t>
+          <t>las mejores hamburguesas en el istmo de tehuantepec</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>mejores lugares para comer frappes frios en el istmo de tehuantepec</t>
+          <t>las mejores hamburguesas en la noche en ixtepec</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>mejores lugares para comer frappes frios en la noche en ixtepec</t>
+          <t>lugares para cenar boneless a domicilio en ixtepec</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>Comparativa</t>
+          <t>Informativa</t>
         </is>
       </c>
       <c r="F97" s="3" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>mejores lugares para comer hamburguesas cerca del parque ixtepec</t>
+          <t>lugares para cenar hamburguesas de arrachera en el istmo</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Comparativa</t>
+          <t>Informativa</t>
         </is>
       </c>
       <c r="F98" s="3" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>mr papas istmo</t>
+          <t>lugares para cenar hamburguesas de arrachera en el istmo de tehuantepec</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>Marca</t>
+          <t>Informativa</t>
         </is>
       </c>
       <c r="F99" s="3" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>mr papas ixtepec</t>
+          <t>lugares para visitar en ixtepec</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
@@ -3487,7 +3487,7 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>Marca</t>
+          <t>Informativa</t>
         </is>
       </c>
       <c r="F100" s="3" t="inlineStr">
@@ -3502,7 +3502,7 @@
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>precio de hamburguesas de arrachera en el istmo</t>
+          <t>mejores lugares para comer alitas bbq para bajar la cruda en el istmo</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>Transaccional</t>
+          <t>Comparativa</t>
         </is>
       </c>
       <c r="F101" s="3" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>precio de hamburguesas en el istmo</t>
+          <t>mejores lugares para comer alitas picosas en ixtepec</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
@@ -3547,7 +3547,7 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>Transaccional</t>
+          <t>Comparativa</t>
         </is>
       </c>
       <c r="F102" s="3" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>promociones de alitas bbq cerca del parque ixtepec</t>
+          <t>mejores lugares para comer frappes frios en el istmo</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
@@ -3577,7 +3577,7 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>Transaccional</t>
+          <t>Comparativa</t>
         </is>
       </c>
       <c r="F103" s="3" t="inlineStr">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>promociones de alitas en ixtepec</t>
+          <t>mejores lugares para comer frappes frios en el istmo de tehuantepec</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
@@ -3607,7 +3607,7 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>Transaccional</t>
+          <t>Comparativa</t>
         </is>
       </c>
       <c r="F104" s="3" t="inlineStr">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>promociones de alitas picosas cerca del parque ixtepec</t>
+          <t>mejores lugares para comer frappes frios en la noche en ixtepec</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>Transaccional</t>
+          <t>Comparativa</t>
         </is>
       </c>
       <c r="F105" s="3" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>promociones de comida para llevar en ciudad ixtepec</t>
+          <t>mejores lugares para comer hamburguesas cerca del parque ixtepec</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
@@ -3667,7 +3667,7 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>Transaccional</t>
+          <t>Comparativa</t>
         </is>
       </c>
       <c r="F106" s="3" t="inlineStr">
@@ -3682,7 +3682,7 @@
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>promociones de frappes frios en ciudad ixtepec</t>
+          <t>mr papas istmo</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>Transaccional</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="F107" s="3" t="inlineStr">
@@ -3712,7 +3712,7 @@
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>promociones de postres a domicilio en ixtepec</t>
+          <t>mr papas ixtepec</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>Transaccional</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="F108" s="3" t="inlineStr">
@@ -3742,7 +3742,7 @@
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>que hacer por la tarde en ixtepec</t>
+          <t>precio de frappes en el istmo</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>Busqueda</t>
+          <t>Transaccional</t>
         </is>
       </c>
       <c r="F109" s="3" t="inlineStr">
@@ -3772,7 +3772,7 @@
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>restaurantes de alitas bbq de madrugada en el istmo</t>
+          <t>precio de frappes en ixtepec</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>Informativa</t>
+          <t>Transaccional</t>
         </is>
       </c>
       <c r="F110" s="3" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>restaurantes de alitas bbq en el istmo de tehuantepec</t>
+          <t>precio de hamburguesas de arrachera en el istmo</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>Informativa</t>
+          <t>Transaccional</t>
         </is>
       </c>
       <c r="F111" s="3" t="inlineStr">
@@ -3832,7 +3832,7 @@
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>restaurantes de alitas en ixtepec</t>
+          <t>precio de hamburguesas en el istmo</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
@@ -3847,7 +3847,7 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>Informativa</t>
+          <t>Transaccional</t>
         </is>
       </c>
       <c r="F112" s="3" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>restaurantes de boneless cerca del parque ixtepec</t>
+          <t>promociones de alitas bbq cerca del parque ixtepec</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
@@ -3877,7 +3877,7 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>Informativa</t>
+          <t>Transaccional</t>
         </is>
       </c>
       <c r="F113" s="3" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>restaurantes de frappes en el istmo de tehuantepec</t>
+          <t>promociones de alitas en el istmo de tehuantepec</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>Informativa</t>
+          <t>Transaccional</t>
         </is>
       </c>
       <c r="F114" s="3" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>restaurantes de frappes frios en la noche en ixtepec</t>
+          <t>promociones de alitas en ixtepec</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>Informativa</t>
+          <t>Transaccional</t>
         </is>
       </c>
       <c r="F115" s="3" t="inlineStr">
@@ -3952,7 +3952,7 @@
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>restaurantes de frappes frios para bajar la cruda en el istmo</t>
+          <t>promociones de comida para llevar en ciudad ixtepec</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>Informativa</t>
+          <t>Transaccional</t>
         </is>
       </c>
       <c r="F116" s="3" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>restaurantes de postres a domicilio en ixtepec</t>
+          <t>promociones de frappes frios en ciudad ixtepec</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>Informativa</t>
+          <t>Transaccional</t>
         </is>
       </c>
       <c r="F117" s="3" t="inlineStr">
@@ -4012,7 +4012,7 @@
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>restaurantes de snacks en el istmo</t>
+          <t>promociones de frappes frios en ixtepec</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>Informativa</t>
+          <t>Transaccional</t>
         </is>
       </c>
       <c r="F118" s="3" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>turismo en ixtepec</t>
+          <t>promociones de hamburguesas de arrachera cerca del parque ixtepec</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
@@ -4057,7 +4057,7 @@
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>Informativa</t>
+          <t>Transaccional</t>
         </is>
       </c>
       <c r="F119" s="3" t="inlineStr">
@@ -4072,17 +4072,17 @@
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>alitas muy picosas del istmo</t>
-        </is>
-      </c>
-      <c r="C120" s="6" t="inlineStr">
-        <is>
-          <t>MEDIO</t>
+          <t>restaurante familiar en el istmo</t>
+        </is>
+      </c>
+      <c r="C120" s="5" t="inlineStr">
+        <is>
+          <t>MEDIO-ALTO</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>20-50</t>
+          <t>50-100</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>Volumen medio</t>
+          <t>Buen volumen moderado</t>
         </is>
       </c>
     </row>
@@ -4102,17 +4102,17 @@
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>alitas y boneless para llevar en ixtepec</t>
-        </is>
-      </c>
-      <c r="C121" s="6" t="inlineStr">
-        <is>
-          <t>MEDIO</t>
+          <t>restaurante familiar en ixtepec</t>
+        </is>
+      </c>
+      <c r="C121" s="5" t="inlineStr">
+        <is>
+          <t>MEDIO-ALTO</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>20-50</t>
+          <t>50-100</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>Volumen medio</t>
+          <t>Buen volumen moderado</t>
         </is>
       </c>
     </row>
@@ -4132,17 +4132,17 @@
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>antojos alitas bbq cerca del parque ixtepec</t>
-        </is>
-      </c>
-      <c r="C122" s="6" t="inlineStr">
-        <is>
-          <t>MEDIO</t>
+          <t>restaurantes de alitas bbq de madrugada en el istmo</t>
+        </is>
+      </c>
+      <c r="C122" s="5" t="inlineStr">
+        <is>
+          <t>MEDIO-ALTO</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>20-50</t>
+          <t>50-100</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -4152,7 +4152,7 @@
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t>Volumen medio</t>
+          <t>Buen volumen moderado</t>
         </is>
       </c>
     </row>
@@ -4162,17 +4162,17 @@
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>antojos alitas bbq en el istmo de tehuantepec</t>
-        </is>
-      </c>
-      <c r="C123" s="6" t="inlineStr">
-        <is>
-          <t>MEDIO</t>
+          <t>restaurantes de alitas bbq en el istmo de tehuantepec</t>
+        </is>
+      </c>
+      <c r="C123" s="5" t="inlineStr">
+        <is>
+          <t>MEDIO-ALTO</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>20-50</t>
+          <t>50-100</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t>Volumen medio</t>
+          <t>Buen volumen moderado</t>
         </is>
       </c>
     </row>
@@ -4192,17 +4192,17 @@
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>antojos alitas bbq para bajar la cruda en el istmo</t>
-        </is>
-      </c>
-      <c r="C124" s="6" t="inlineStr">
-        <is>
-          <t>MEDIO</t>
+          <t>restaurantes de boneless cerca del parque ixtepec</t>
+        </is>
+      </c>
+      <c r="C124" s="5" t="inlineStr">
+        <is>
+          <t>MEDIO-ALTO</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>20-50</t>
+          <t>50-100</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
@@ -4212,7 +4212,7 @@
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>Volumen medio</t>
+          <t>Buen volumen moderado</t>
         </is>
       </c>
     </row>
@@ -4222,17 +4222,17 @@
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>antojos alitas picosas cerca del parque ixtepec</t>
-        </is>
-      </c>
-      <c r="C125" s="6" t="inlineStr">
-        <is>
-          <t>MEDIO</t>
+          <t>restaurantes de comida para llevar en ixtepec</t>
+        </is>
+      </c>
+      <c r="C125" s="5" t="inlineStr">
+        <is>
+          <t>MEDIO-ALTO</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>20-50</t>
+          <t>50-100</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
@@ -4242,7 +4242,7 @@
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>Volumen medio</t>
+          <t>Buen volumen moderado</t>
         </is>
       </c>
     </row>
@@ -4252,17 +4252,17 @@
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>antojos alitas picosas de madrugada en el istmo</t>
-        </is>
-      </c>
-      <c r="C126" s="6" t="inlineStr">
-        <is>
-          <t>MEDIO</t>
+          <t>restaurantes de frappes frios en la noche en ixtepec</t>
+        </is>
+      </c>
+      <c r="C126" s="5" t="inlineStr">
+        <is>
+          <t>MEDIO-ALTO</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>20-50</t>
+          <t>50-100</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>Volumen medio</t>
+          <t>Buen volumen moderado</t>
         </is>
       </c>
     </row>
@@ -4282,17 +4282,17 @@
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>antojos alitas picosas en el istmo de tehuantepec</t>
-        </is>
-      </c>
-      <c r="C127" s="6" t="inlineStr">
-        <is>
-          <t>MEDIO</t>
+          <t>restaurantes de papas con queso en ciudad ixtepec</t>
+        </is>
+      </c>
+      <c r="C127" s="5" t="inlineStr">
+        <is>
+          <t>MEDIO-ALTO</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>20-50</t>
+          <t>50-100</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
@@ -4302,7 +4302,7 @@
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>Volumen medio</t>
+          <t>Buen volumen moderado</t>
         </is>
       </c>
     </row>
@@ -4312,17 +4312,17 @@
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>antojos boneless de madrugada en el istmo</t>
-        </is>
-      </c>
-      <c r="C128" s="6" t="inlineStr">
-        <is>
-          <t>MEDIO</t>
+          <t>restaurantes de papas con queso en la noche en ixtepec</t>
+        </is>
+      </c>
+      <c r="C128" s="5" t="inlineStr">
+        <is>
+          <t>MEDIO-ALTO</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>20-50</t>
+          <t>50-100</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>Volumen medio</t>
+          <t>Buen volumen moderado</t>
         </is>
       </c>
     </row>
@@ -4342,17 +4342,17 @@
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>antojos comida para llevar en la noche en ixtepec</t>
-        </is>
-      </c>
-      <c r="C129" s="6" t="inlineStr">
-        <is>
-          <t>MEDIO</t>
+          <t>restaurantes de postres a domicilio en ixtepec</t>
+        </is>
+      </c>
+      <c r="C129" s="5" t="inlineStr">
+        <is>
+          <t>MEDIO-ALTO</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>20-50</t>
+          <t>50-100</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>Volumen medio</t>
+          <t>Buen volumen moderado</t>
         </is>
       </c>
     </row>
@@ -4372,17 +4372,17 @@
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>antojos papas a la francesa en la noche en ixtepec</t>
-        </is>
-      </c>
-      <c r="C130" s="6" t="inlineStr">
-        <is>
-          <t>MEDIO</t>
+          <t>turismo en ixtepec</t>
+        </is>
+      </c>
+      <c r="C130" s="5" t="inlineStr">
+        <is>
+          <t>MEDIO-ALTO</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>20-50</t>
+          <t>50-100</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>Volumen medio</t>
+          <t>Buen volumen moderado</t>
         </is>
       </c>
     </row>
@@ -4402,7 +4402,7 @@
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>bebidas para el calor en ixtepec</t>
+          <t>alitas a domicilio en ixtepec</t>
         </is>
       </c>
       <c r="C131" s="6" t="inlineStr">
@@ -4432,7 +4432,7 @@
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>cenadurias con papas a la francesa en ixtepec</t>
+          <t>alitas picosas en el istmo</t>
         </is>
       </c>
       <c r="C132" s="6" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>combo familiar de alitas en el istmo</t>
+          <t>alitas y boneless para llevar en ixtepec</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr">
@@ -4492,7 +4492,7 @@
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>comida a domicilio de noche en ixtepec</t>
+          <t>antojos alitas bbq cerca del parque ixtepec</t>
         </is>
       </c>
       <c r="C134" s="6" t="inlineStr">
@@ -4522,7 +4522,7 @@
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>comida para jovenes en el istmo</t>
+          <t>antojos alitas bbq en el istmo de tehuantepec</t>
         </is>
       </c>
       <c r="C135" s="6" t="inlineStr">
@@ -4552,7 +4552,7 @@
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>comida para reuniones en el istmo</t>
+          <t>antojos alitas picosas en el istmo de tehuantepec</t>
         </is>
       </c>
       <c r="C136" s="6" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>comida para ver el partido</t>
+          <t>bebidas frias en el istmo</t>
         </is>
       </c>
       <c r="C137" s="6" t="inlineStr">
@@ -4612,7 +4612,7 @@
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>comida rapida loaded fries cerca del parque ixtepec</t>
+          <t>boneless con salsa en ixtepec</t>
         </is>
       </c>
       <c r="C138" s="6" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>comida rapida papas con queso para bajar la cruda en el istmo</t>
+          <t>boneless por kilo en el istmo</t>
         </is>
       </c>
       <c r="C139" s="6" t="inlineStr">
@@ -4672,7 +4672,7 @@
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>donde celebrar cumplea±os en ixtepec</t>
+          <t>cenadurias con papas a la francesa en ixtepec</t>
         </is>
       </c>
       <c r="C140" s="6" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>Busqueda</t>
+          <t>Informativa</t>
         </is>
       </c>
       <c r="F140" s="3" t="inlineStr">
@@ -4702,7 +4702,7 @@
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>donde cenar cenas baratas cerca del parque ixtepec</t>
+          <t>cenar rico y barato en ixtepec</t>
         </is>
       </c>
       <c r="C141" s="6" t="inlineStr">
@@ -4717,7 +4717,7 @@
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>Busqueda</t>
+          <t>Informativa</t>
         </is>
       </c>
       <c r="F141" s="3" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>donde cenar cenas baratas en ciudad ixtepec</t>
+          <t>comida a domicilio de noche en ixtepec</t>
         </is>
       </c>
       <c r="C142" s="6" t="inlineStr">
@@ -4747,7 +4747,7 @@
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>Busqueda</t>
+          <t>Informativa</t>
         </is>
       </c>
       <c r="F142" s="3" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>donde comer botanas cerca del parque ixtepec</t>
+          <t>comida cerca de mi en el istmo</t>
         </is>
       </c>
       <c r="C143" s="6" t="inlineStr">
@@ -4777,7 +4777,7 @@
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>Busqueda</t>
+          <t>Informativa</t>
         </is>
       </c>
       <c r="F143" s="3" t="inlineStr">
@@ -4792,7 +4792,7 @@
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>donde comer botanas en ciudad ixtepec</t>
+          <t>comida para fiestas en ixtepec</t>
         </is>
       </c>
       <c r="C144" s="6" t="inlineStr">
@@ -4807,7 +4807,7 @@
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>Busqueda</t>
+          <t>Informativa</t>
         </is>
       </c>
       <c r="F144" s="3" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>donde comer papas con queso de madrugada en el istmo</t>
+          <t>comida para ver el partido</t>
         </is>
       </c>
       <c r="C145" s="6" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>Busqueda</t>
+          <t>Informativa</t>
         </is>
       </c>
       <c r="F145" s="3" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>donde comprar alitas bbq en el istmo de tehuantepec</t>
+          <t>comida rapida abierta de noche en ixtepec</t>
         </is>
       </c>
       <c r="C146" s="6" t="inlineStr">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>Busqueda</t>
+          <t>Informativa</t>
         </is>
       </c>
       <c r="F146" s="3" t="inlineStr">
@@ -4882,7 +4882,7 @@
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>donde comprar alitas en ixtepec</t>
+          <t>comida rapida papas a la francesa para bajar la cruda en el istmo</t>
         </is>
       </c>
       <c r="C147" s="6" t="inlineStr">
@@ -4897,7 +4897,7 @@
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>Busqueda</t>
+          <t>Informativa</t>
         </is>
       </c>
       <c r="F147" s="3" t="inlineStr">
@@ -4912,7 +4912,7 @@
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>donde comprar boneless por kilo en ixtepec</t>
+          <t>comida rapida papas con queso para bajar la cruda en el istmo</t>
         </is>
       </c>
       <c r="C148" s="6" t="inlineStr">
@@ -4927,7 +4927,7 @@
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>Busqueda</t>
+          <t>Informativa</t>
         </is>
       </c>
       <c r="F148" s="3" t="inlineStr">
@@ -4942,7 +4942,7 @@
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>donde comprar papas con queso a domicilio en ixtepec</t>
+          <t>donde cenar cenas baratas cerca del parque ixtepec</t>
         </is>
       </c>
       <c r="C149" s="6" t="inlineStr">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>donde ir a comer en el dia del ni±o en ixtepec</t>
+          <t>donde cenar cenas baratas en ciudad ixtepec</t>
         </is>
       </c>
       <c r="C150" s="6" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>donde llevar a mi novia en ixtepec</t>
+          <t>donde comer botanas en ciudad ixtepec</t>
         </is>
       </c>
       <c r="C151" s="6" t="inlineStr">
@@ -5032,7 +5032,7 @@
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>donde pedir alitas bbq de madrugada en el istmo</t>
+          <t>donde comer papas con queso de madrugada en el istmo</t>
         </is>
       </c>
       <c r="C152" s="6" t="inlineStr">
@@ -5062,7 +5062,7 @@
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>donde pedir alitas para fiestas en ixtepec</t>
+          <t>donde comprar alitas bbq en el istmo de tehuantepec</t>
         </is>
       </c>
       <c r="C153" s="6" t="inlineStr">
@@ -5092,7 +5092,7 @@
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>donde pedir alitas picosas en ciudad ixtepec</t>
+          <t>donde comprar alitas en ixtepec</t>
         </is>
       </c>
       <c r="C154" s="6" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>donde pedir cenas baratas a domicilio en ixtepec</t>
+          <t>donde comprar boneless por kilo en ixtepec</t>
         </is>
       </c>
       <c r="C155" s="6" t="inlineStr">
@@ -5152,7 +5152,7 @@
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>donde pedir frappes de madrugada en el istmo</t>
+          <t>donde comprar comida para llevar a domicilio en ixtepec</t>
         </is>
       </c>
       <c r="C156" s="6" t="inlineStr">
@@ -5182,7 +5182,7 @@
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>donde pedir hamburguesas para bajar la cruda en el istmo</t>
+          <t>donde comprar hamburguesas de arrachera de madrugada en el istmo</t>
         </is>
       </c>
       <c r="C157" s="6" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>donde pedir papas con queso a domicilio en ixtepec</t>
+          <t>donde comprar papas con queso a domicilio en ixtepec</t>
         </is>
       </c>
       <c r="C158" s="6" t="inlineStr">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>donde pedir postres a domicilio en ixtepec</t>
+          <t>donde ir a comer en el dia del ni±o en ixtepec</t>
         </is>
       </c>
       <c r="C159" s="6" t="inlineStr">
@@ -5272,7 +5272,7 @@
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>donde salir a comer botanas en el istmo</t>
+          <t>donde llevar a mi novia en ixtepec</t>
         </is>
       </c>
       <c r="C160" s="6" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>donde salir a comer loaded fries en ixtepec</t>
+          <t>donde pedir alitas en ciudad ixtepec</t>
         </is>
       </c>
       <c r="C161" s="6" t="inlineStr">
@@ -5332,7 +5332,7 @@
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>donde venden alitas en ixtepec</t>
+          <t>donde pedir alitas para fiestas en ixtepec</t>
         </is>
       </c>
       <c r="C162" s="6" t="inlineStr">
@@ -5362,7 +5362,7 @@
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>donde venden alitas picosas en ciudad ixtepec</t>
+          <t>donde pedir alitas picosas en ciudad ixtepec</t>
         </is>
       </c>
       <c r="C163" s="6" t="inlineStr">
@@ -5392,7 +5392,7 @@
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>donde venden alitas picosas en la noche en ixtepec</t>
+          <t>donde pedir cenas baratas a domicilio en ixtepec</t>
         </is>
       </c>
       <c r="C164" s="6" t="inlineStr">
@@ -5422,7 +5422,7 @@
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>donde venden boneless en la noche en ixtepec</t>
+          <t>donde pedir conos de boneless a domicilio en ixtepec</t>
         </is>
       </c>
       <c r="C165" s="6" t="inlineStr">
@@ -5452,7 +5452,7 @@
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>donde venden frappes frios en la noche en ixtepec</t>
+          <t>donde pedir papas con queso a domicilio en ixtepec</t>
         </is>
       </c>
       <c r="C166" s="6" t="inlineStr">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>donde ver el partido de futbol en el istmo</t>
+          <t>donde pedir papas con queso en ixtepec</t>
         </is>
       </c>
       <c r="C167" s="6" t="inlineStr">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>frappe de capuchino istmo</t>
+          <t>donde salir a comer botanas en el istmo</t>
         </is>
       </c>
       <c r="C168" s="6" t="inlineStr">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>Informativa</t>
+          <t>Busqueda</t>
         </is>
       </c>
       <c r="F168" s="3" t="inlineStr">
@@ -5542,7 +5542,7 @@
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>frappe de mazapan ixtepec</t>
+          <t>donde salir a comer comida para llevar cerca del parque ixtepec</t>
         </is>
       </c>
       <c r="C169" s="6" t="inlineStr">
@@ -5557,7 +5557,7 @@
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>Informativa</t>
+          <t>Busqueda</t>
         </is>
       </c>
       <c r="F169" s="3" t="inlineStr">
@@ -5572,7 +5572,7 @@
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>las mejores alitas en el istmo</t>
+          <t>donde salir a comer comida para llevar de madrugada en el istmo</t>
         </is>
       </c>
       <c r="C170" s="6" t="inlineStr">
@@ -5587,7 +5587,7 @@
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>Comparativa</t>
+          <t>Busqueda</t>
         </is>
       </c>
       <c r="F170" s="3" t="inlineStr">
@@ -5602,7 +5602,7 @@
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>las mejores frappes de madrugada en el istmo</t>
+          <t>donde salir a comer en el istmo</t>
         </is>
       </c>
       <c r="C171" s="6" t="inlineStr">
@@ -5617,7 +5617,7 @@
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>Comparativa</t>
+          <t>Busqueda</t>
         </is>
       </c>
       <c r="F171" s="3" t="inlineStr">
@@ -5632,7 +5632,7 @@
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>las mejores hamburguesas en el istmo de tehuantepec</t>
+          <t>donde salir a comer loaded fries en ixtepec</t>
         </is>
       </c>
       <c r="C172" s="6" t="inlineStr">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>Comparativa</t>
+          <t>Busqueda</t>
         </is>
       </c>
       <c r="F172" s="3" t="inlineStr">
@@ -5662,7 +5662,7 @@
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>las mejores hamburguesas para bajar la cruda en el istmo</t>
+          <t>donde venden alitas en ixtepec</t>
         </is>
       </c>
       <c r="C173" s="6" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>Comparativa</t>
+          <t>Busqueda</t>
         </is>
       </c>
       <c r="F173" s="3" t="inlineStr">
@@ -5692,7 +5692,7 @@
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>lugar mas barato para comer en ixtepec</t>
+          <t>donde venden alitas picosas en ciudad ixtepec</t>
         </is>
       </c>
       <c r="C174" s="6" t="inlineStr">
@@ -5707,7 +5707,7 @@
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>Informativa</t>
+          <t>Busqueda</t>
         </is>
       </c>
       <c r="F174" s="3" t="inlineStr">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>lugares para cenar alitas bbq para bajar la cruda en el istmo</t>
+          <t>el mejor lugar para comer en el istmo</t>
         </is>
       </c>
       <c r="C175" s="6" t="inlineStr">
@@ -5737,7 +5737,7 @@
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>Informativa</t>
+          <t>Comparativa</t>
         </is>
       </c>
       <c r="F175" s="3" t="inlineStr">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="B176" s="3" t="inlineStr">
         <is>
-          <t>lugares para cenar alitas picosas en la noche en ixtepec</t>
+          <t>el mejor lugar para comer en ixtepec</t>
         </is>
       </c>
       <c r="C176" s="6" t="inlineStr">
@@ -5767,7 +5767,7 @@
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>Informativa</t>
+          <t>Comparativa</t>
         </is>
       </c>
       <c r="F176" s="3" t="inlineStr">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="B177" s="3" t="inlineStr">
         <is>
-          <t>lugares para cenar hamburguesas cerca del parque ixtepec</t>
+          <t>frappe de capuchino en ixtepec</t>
         </is>
       </c>
       <c r="C177" s="6" t="inlineStr">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="B178" s="3" t="inlineStr">
         <is>
-          <t>mejor frappe de mazapan en ixtepec</t>
+          <t>frappe de mazapan en ixtepec</t>
         </is>
       </c>
       <c r="C178" s="6" t="inlineStr">
@@ -5827,7 +5827,7 @@
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>Comparativa</t>
+          <t>Informativa</t>
         </is>
       </c>
       <c r="F178" s="3" t="inlineStr">
@@ -5842,7 +5842,7 @@
       </c>
       <c r="B179" s="3" t="inlineStr">
         <is>
-          <t>mejores lugares para comer cenas baratas en ciudad ixtepec</t>
+          <t>frappe de moka en ixtepec</t>
         </is>
       </c>
       <c r="C179" s="6" t="inlineStr">
@@ -5857,7 +5857,7 @@
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>Comparativa</t>
+          <t>Informativa</t>
         </is>
       </c>
       <c r="F179" s="3" t="inlineStr">
@@ -5872,7 +5872,7 @@
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>paquetes de alitas para eventos en ixtepec</t>
+          <t>frappe de oreo en ixtepec</t>
         </is>
       </c>
       <c r="C180" s="6" t="inlineStr">
@@ -5902,7 +5902,7 @@
       </c>
       <c r="B181" s="3" t="inlineStr">
         <is>
-          <t>paquetes de comida para eventos en el istmo</t>
+          <t>hamburguesa de arrachera a domicilio ixtepec</t>
         </is>
       </c>
       <c r="C181" s="6" t="inlineStr">
@@ -5932,7 +5932,7 @@
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>precio de alitas picosas en ixtepec</t>
+          <t>hamburguesas gigantes y jugosas en el istmo</t>
         </is>
       </c>
       <c r="C182" s="6" t="inlineStr">
@@ -5947,7 +5947,7 @@
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>Transaccional</t>
+          <t>Informativa</t>
         </is>
       </c>
       <c r="F182" s="3" t="inlineStr">
@@ -5962,7 +5962,7 @@
       </c>
       <c r="B183" s="3" t="inlineStr">
         <is>
-          <t>precio de comida para llevar en ixtepec</t>
+          <t>las mejores alitas en el istmo</t>
         </is>
       </c>
       <c r="C183" s="6" t="inlineStr">
@@ -5977,7 +5977,7 @@
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>Transaccional</t>
+          <t>Comparativa</t>
         </is>
       </c>
       <c r="F183" s="3" t="inlineStr">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="B184" s="3" t="inlineStr">
         <is>
-          <t>precio de frappes en el istmo</t>
+          <t>las mejores papas a la francesa a domicilio en ixtepec</t>
         </is>
       </c>
       <c r="C184" s="6" t="inlineStr">
@@ -6007,7 +6007,7 @@
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>Transaccional</t>
+          <t>Comparativa</t>
         </is>
       </c>
       <c r="F184" s="3" t="inlineStr">
@@ -6022,7 +6022,7 @@
       </c>
       <c r="B185" s="3" t="inlineStr">
         <is>
-          <t>precio de frappes en ixtepec</t>
+          <t>lugar mas barato para comer en ixtepec</t>
         </is>
       </c>
       <c r="C185" s="6" t="inlineStr">
@@ -6037,7 +6037,7 @@
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>Transaccional</t>
+          <t>Informativa</t>
         </is>
       </c>
       <c r="F185" s="3" t="inlineStr">
@@ -6052,7 +6052,7 @@
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>precio de hamburguesas de arrachera en el istmo de tehuantepec</t>
+          <t>lugares para cenar hamburguesas cerca del parque ixtepec</t>
         </is>
       </c>
       <c r="C186" s="6" t="inlineStr">
@@ -6067,7 +6067,7 @@
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>Transaccional</t>
+          <t>Informativa</t>
         </is>
       </c>
       <c r="F186" s="3" t="inlineStr">
@@ -6082,7 +6082,7 @@
       </c>
       <c r="B187" s="3" t="inlineStr">
         <is>
-          <t>promociones de alitas en el istmo de tehuantepec</t>
+          <t>mejor frappe de mazapan en ixtepec</t>
         </is>
       </c>
       <c r="C187" s="6" t="inlineStr">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>Transaccional</t>
+          <t>Comparativa</t>
         </is>
       </c>
       <c r="F187" s="3" t="inlineStr">
@@ -6112,7 +6112,7 @@
       </c>
       <c r="B188" s="3" t="inlineStr">
         <is>
-          <t>promociones de alitas picosas en el istmo de tehuantepec</t>
+          <t>mejor lugar para ir a comer en familia en el istmo</t>
         </is>
       </c>
       <c r="C188" s="6" t="inlineStr">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>Transaccional</t>
+          <t>Comparativa</t>
         </is>
       </c>
       <c r="F188" s="3" t="inlineStr">
@@ -6142,7 +6142,7 @@
       </c>
       <c r="B189" s="3" t="inlineStr">
         <is>
-          <t>promociones de conos de boneless de madrugada en el istmo</t>
+          <t>mejor lugar para ir a comer en familia en ixtepec</t>
         </is>
       </c>
       <c r="C189" s="6" t="inlineStr">
@@ -6157,7 +6157,7 @@
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>Transaccional</t>
+          <t>Comparativa</t>
         </is>
       </c>
       <c r="F189" s="3" t="inlineStr">
@@ -6172,7 +6172,7 @@
       </c>
       <c r="B190" s="3" t="inlineStr">
         <is>
-          <t>promociones de loaded fries en el istmo</t>
+          <t>mejores lugares para comer alitas picosas cerca del parque ixtepec</t>
         </is>
       </c>
       <c r="C190" s="6" t="inlineStr">
@@ -6187,7 +6187,7 @@
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>Transaccional</t>
+          <t>Comparativa</t>
         </is>
       </c>
       <c r="F190" s="3" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="B191" s="3" t="inlineStr">
         <is>
-          <t>que comer en el istmo</t>
+          <t>mejores lugares para comer botanas a domicilio en ixtepec</t>
         </is>
       </c>
       <c r="C191" s="6" t="inlineStr">
@@ -6217,7 +6217,7 @@
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>Informativa</t>
+          <t>Comparativa</t>
         </is>
       </c>
       <c r="F191" s="3" t="inlineStr">
@@ -6232,7 +6232,7 @@
       </c>
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t>restaurantes de alitas de madrugada en el istmo</t>
+          <t>mejores lugares para comer cenas baratas en ciudad ixtepec</t>
         </is>
       </c>
       <c r="C192" s="6" t="inlineStr">
@@ -6247,7 +6247,7 @@
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>Informativa</t>
+          <t>Comparativa</t>
         </is>
       </c>
       <c r="F192" s="3" t="inlineStr">
@@ -6262,7 +6262,7 @@
       </c>
       <c r="B193" s="3" t="inlineStr">
         <is>
-          <t>restaurantes de cenas baratas cerca del parque ixtepec</t>
+          <t>mejores lugares para comer comida para llevar cerca del parque ixtepec</t>
         </is>
       </c>
       <c r="C193" s="6" t="inlineStr">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>Informativa</t>
+          <t>Comparativa</t>
         </is>
       </c>
       <c r="F193" s="3" t="inlineStr">
@@ -6292,7 +6292,7 @@
       </c>
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>restaurantes de papas con queso en ciudad ixtepec</t>
+          <t>papas a la francesa en el istmo</t>
         </is>
       </c>
       <c r="C194" s="6" t="inlineStr">
@@ -6322,7 +6322,7 @@
       </c>
       <c r="B195" s="3" t="inlineStr">
         <is>
-          <t>restaurantes de papas con queso en la noche en ixtepec</t>
+          <t>papas a la francesa en ixtepec</t>
         </is>
       </c>
       <c r="C195" s="6" t="inlineStr">
@@ -6352,17 +6352,17 @@
       </c>
       <c r="B196" s="3" t="inlineStr">
         <is>
-          <t>antojos papas a la francesa cerca del parque ixtepec</t>
-        </is>
-      </c>
-      <c r="C196" s="7" t="inlineStr">
-        <is>
-          <t>MEDIO-BAJO</t>
+          <t>papas con queso en el istmo</t>
+        </is>
+      </c>
+      <c r="C196" s="6" t="inlineStr">
+        <is>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>10-20</t>
+          <t>20-50</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
@@ -6372,7 +6372,7 @@
       </c>
       <c r="F196" s="3" t="inlineStr">
         <is>
-          <t>Bajo pero relevante</t>
+          <t>Volumen medio</t>
         </is>
       </c>
     </row>
@@ -6382,17 +6382,17 @@
       </c>
       <c r="B197" s="3" t="inlineStr">
         <is>
-          <t>antojos papas a la francesa para bajar la cruda en el istmo</t>
-        </is>
-      </c>
-      <c r="C197" s="7" t="inlineStr">
-        <is>
-          <t>MEDIO-BAJO</t>
+          <t>papas con queso en ixtepec</t>
+        </is>
+      </c>
+      <c r="C197" s="6" t="inlineStr">
+        <is>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>10-20</t>
+          <t>20-50</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
@@ -6402,7 +6402,7 @@
       </c>
       <c r="F197" s="3" t="inlineStr">
         <is>
-          <t>Bajo pero relevante</t>
+          <t>Volumen medio</t>
         </is>
       </c>
     </row>
@@ -6412,17 +6412,17 @@
       </c>
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>cenadurias con papas a la francesa para bajar la cruda en el istmo</t>
-        </is>
-      </c>
-      <c r="C198" s="7" t="inlineStr">
-        <is>
-          <t>MEDIO-BAJO</t>
+          <t>papas con queso y tocino en ixtepec</t>
+        </is>
+      </c>
+      <c r="C198" s="6" t="inlineStr">
+        <is>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>10-20</t>
+          <t>20-50</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
@@ -6432,7 +6432,7 @@
       </c>
       <c r="F198" s="3" t="inlineStr">
         <is>
-          <t>Bajo pero relevante</t>
+          <t>Volumen medio</t>
         </is>
       </c>
     </row>
@@ -6442,17 +6442,17 @@
       </c>
       <c r="B199" s="3" t="inlineStr">
         <is>
-          <t>comida rapida loaded fries en el istmo de tehuantepec</t>
-        </is>
-      </c>
-      <c r="C199" s="7" t="inlineStr">
-        <is>
-          <t>MEDIO-BAJO</t>
+          <t>papas con tocino en el istmo</t>
+        </is>
+      </c>
+      <c r="C199" s="6" t="inlineStr">
+        <is>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>10-20</t>
+          <t>20-50</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="F199" s="3" t="inlineStr">
         <is>
-          <t>Bajo pero relevante</t>
+          <t>Volumen medio</t>
         </is>
       </c>
     </row>
@@ -6472,27 +6472,27 @@
       </c>
       <c r="B200" s="3" t="inlineStr">
         <is>
-          <t>donde comer botanas para bajar la cruda en el istmo</t>
-        </is>
-      </c>
-      <c r="C200" s="7" t="inlineStr">
-        <is>
-          <t>MEDIO-BAJO</t>
+          <t>papas con tocino en ixtepec</t>
+        </is>
+      </c>
+      <c r="C200" s="6" t="inlineStr">
+        <is>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>10-20</t>
+          <t>20-50</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>Busqueda</t>
+          <t>Informativa</t>
         </is>
       </c>
       <c r="F200" s="3" t="inlineStr">
         <is>
-          <t>Bajo pero relevante</t>
+          <t>Volumen medio</t>
         </is>
       </c>
     </row>
@@ -6502,27 +6502,27 @@
       </c>
       <c r="B201" s="3" t="inlineStr">
         <is>
-          <t>donde comer loaded fries para bajar la cruda en el istmo</t>
-        </is>
-      </c>
-      <c r="C201" s="7" t="inlineStr">
-        <is>
-          <t>MEDIO-BAJO</t>
+          <t>paquetes de alitas para eventos en ixtepec</t>
+        </is>
+      </c>
+      <c r="C201" s="6" t="inlineStr">
+        <is>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>10-20</t>
+          <t>20-50</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>Busqueda</t>
+          <t>Informativa</t>
         </is>
       </c>
       <c r="F201" s="3" t="inlineStr">
         <is>
-          <t>Bajo pero relevante</t>
+          <t>Volumen medio</t>
         </is>
       </c>
     </row>
@@ -6532,27 +6532,27 @@
       </c>
       <c r="B202" s="3" t="inlineStr">
         <is>
-          <t>donde comer snacks para bajar la cruda en el istmo</t>
-        </is>
-      </c>
-      <c r="C202" s="7" t="inlineStr">
-        <is>
-          <t>MEDIO-BAJO</t>
+          <t>paquetes de comida para eventos en el istmo</t>
+        </is>
+      </c>
+      <c r="C202" s="6" t="inlineStr">
+        <is>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>10-20</t>
+          <t>20-50</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>Busqueda</t>
+          <t>Informativa</t>
         </is>
       </c>
       <c r="F202" s="3" t="inlineStr">
         <is>
-          <t>Bajo pero relevante</t>
+          <t>Volumen medio</t>
         </is>
       </c>
     </row>
@@ -6562,27 +6562,27 @@
       </c>
       <c r="B203" s="3" t="inlineStr">
         <is>
-          <t>donde comprar boneless para bajar la cruda en el istmo</t>
-        </is>
-      </c>
-      <c r="C203" s="7" t="inlineStr">
-        <is>
-          <t>MEDIO-BAJO</t>
+          <t>precio de alitas picosas en ixtepec</t>
+        </is>
+      </c>
+      <c r="C203" s="6" t="inlineStr">
+        <is>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>10-20</t>
+          <t>20-50</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>Busqueda</t>
+          <t>Transaccional</t>
         </is>
       </c>
       <c r="F203" s="3" t="inlineStr">
         <is>
-          <t>Bajo pero relevante</t>
+          <t>Volumen medio</t>
         </is>
       </c>
     </row>
@@ -6592,27 +6592,27 @@
       </c>
       <c r="B204" s="3" t="inlineStr">
         <is>
-          <t>donde pedir alitas en ciudad ixtepec</t>
-        </is>
-      </c>
-      <c r="C204" s="7" t="inlineStr">
-        <is>
-          <t>MEDIO-BAJO</t>
+          <t>precio de boneless en el istmo de tehuantepec</t>
+        </is>
+      </c>
+      <c r="C204" s="6" t="inlineStr">
+        <is>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>10-20</t>
+          <t>20-50</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>Busqueda</t>
+          <t>Transaccional</t>
         </is>
       </c>
       <c r="F204" s="3" t="inlineStr">
         <is>
-          <t>Bajo pero relevante</t>
+          <t>Volumen medio</t>
         </is>
       </c>
     </row>
@@ -6622,27 +6622,27 @@
       </c>
       <c r="B205" s="3" t="inlineStr">
         <is>
-          <t>donde pedir comida para llevar cerca del parque ixtepec</t>
-        </is>
-      </c>
-      <c r="C205" s="7" t="inlineStr">
-        <is>
-          <t>MEDIO-BAJO</t>
+          <t>precio de conos de boneless en el istmo de tehuantepec</t>
+        </is>
+      </c>
+      <c r="C205" s="6" t="inlineStr">
+        <is>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>10-20</t>
+          <t>20-50</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>Busqueda</t>
+          <t>Transaccional</t>
         </is>
       </c>
       <c r="F205" s="3" t="inlineStr">
         <is>
-          <t>Bajo pero relevante</t>
+          <t>Volumen medio</t>
         </is>
       </c>
     </row>
@@ -6652,27 +6652,27 @@
       </c>
       <c r="B206" s="3" t="inlineStr">
         <is>
-          <t>donde pedir comida para llevar para bajar la cruda en el istmo</t>
-        </is>
-      </c>
-      <c r="C206" s="7" t="inlineStr">
-        <is>
-          <t>MEDIO-BAJO</t>
+          <t>precio de hamburguesas de arrachera en el istmo de tehuantepec</t>
+        </is>
+      </c>
+      <c r="C206" s="6" t="inlineStr">
+        <is>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>10-20</t>
+          <t>20-50</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>Busqueda</t>
+          <t>Transaccional</t>
         </is>
       </c>
       <c r="F206" s="3" t="inlineStr">
         <is>
-          <t>Bajo pero relevante</t>
+          <t>Volumen medio</t>
         </is>
       </c>
     </row>
@@ -6682,27 +6682,27 @@
       </c>
       <c r="B207" s="3" t="inlineStr">
         <is>
-          <t>donde pedir papas a la francesa en el istmo de tehuantepec</t>
-        </is>
-      </c>
-      <c r="C207" s="7" t="inlineStr">
-        <is>
-          <t>MEDIO-BAJO</t>
+          <t>promociones de alitas picosas cerca del parque ixtepec</t>
+        </is>
+      </c>
+      <c r="C207" s="6" t="inlineStr">
+        <is>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>10-20</t>
+          <t>20-50</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>Busqueda</t>
+          <t>Transaccional</t>
         </is>
       </c>
       <c r="F207" s="3" t="inlineStr">
         <is>
-          <t>Bajo pero relevante</t>
+          <t>Volumen medio</t>
         </is>
       </c>
     </row>
@@ -6712,27 +6712,27 @@
       </c>
       <c r="B208" s="3" t="inlineStr">
         <is>
-          <t>donde pedir papas con queso en ixtepec</t>
-        </is>
-      </c>
-      <c r="C208" s="7" t="inlineStr">
-        <is>
-          <t>MEDIO-BAJO</t>
+          <t>promociones de alitas picosas en el istmo de tehuantepec</t>
+        </is>
+      </c>
+      <c r="C208" s="6" t="inlineStr">
+        <is>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>10-20</t>
+          <t>20-50</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>Busqueda</t>
+          <t>Transaccional</t>
         </is>
       </c>
       <c r="F208" s="3" t="inlineStr">
         <is>
-          <t>Bajo pero relevante</t>
+          <t>Volumen medio</t>
         </is>
       </c>
     </row>
@@ -6742,27 +6742,27 @@
       </c>
       <c r="B209" s="3" t="inlineStr">
         <is>
-          <t>donde venden comida para llevar para bajar la cruda en el istmo</t>
-        </is>
-      </c>
-      <c r="C209" s="7" t="inlineStr">
-        <is>
-          <t>MEDIO-BAJO</t>
+          <t>promociones de conos de boneless de madrugada en el istmo</t>
+        </is>
+      </c>
+      <c r="C209" s="6" t="inlineStr">
+        <is>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>10-20</t>
+          <t>20-50</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>Busqueda</t>
+          <t>Transaccional</t>
         </is>
       </c>
       <c r="F209" s="3" t="inlineStr">
         <is>
-          <t>Bajo pero relevante</t>
+          <t>Volumen medio</t>
         </is>
       </c>
     </row>
@@ -6772,27 +6772,27 @@
       </c>
       <c r="B210" s="3" t="inlineStr">
         <is>
-          <t>donde venden frappes frios para bajar la cruda en el istmo</t>
-        </is>
-      </c>
-      <c r="C210" s="7" t="inlineStr">
-        <is>
-          <t>MEDIO-BAJO</t>
+          <t>promociones de papas con queso cerca del parque ixtepec</t>
+        </is>
+      </c>
+      <c r="C210" s="6" t="inlineStr">
+        <is>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>10-20</t>
+          <t>20-50</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>Busqueda</t>
+          <t>Transaccional</t>
         </is>
       </c>
       <c r="F210" s="3" t="inlineStr">
         <is>
-          <t>Bajo pero relevante</t>
+          <t>Volumen medio</t>
         </is>
       </c>
     </row>
@@ -6802,27 +6802,27 @@
       </c>
       <c r="B211" s="3" t="inlineStr">
         <is>
-          <t>las mejores loaded fries en ixtepec</t>
-        </is>
-      </c>
-      <c r="C211" s="7" t="inlineStr">
-        <is>
-          <t>MEDIO-BAJO</t>
+          <t>promociones de postres a domicilio en ixtepec</t>
+        </is>
+      </c>
+      <c r="C211" s="6" t="inlineStr">
+        <is>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>10-20</t>
+          <t>20-50</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>Comparativa</t>
+          <t>Transaccional</t>
         </is>
       </c>
       <c r="F211" s="3" t="inlineStr">
         <is>
-          <t>Bajo pero relevante</t>
+          <t>Volumen medio</t>
         </is>
       </c>
     </row>
@@ -6832,27 +6832,27 @@
       </c>
       <c r="B212" s="3" t="inlineStr">
         <is>
-          <t>lugares para cenar conos de boneless de madrugada en el istmo</t>
-        </is>
-      </c>
-      <c r="C212" s="7" t="inlineStr">
-        <is>
-          <t>MEDIO-BAJO</t>
+          <t>que comer hoy en ixtepec</t>
+        </is>
+      </c>
+      <c r="C212" s="6" t="inlineStr">
+        <is>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>10-20</t>
+          <t>20-50</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>Informativa</t>
+          <t>Busqueda</t>
         </is>
       </c>
       <c r="F212" s="3" t="inlineStr">
         <is>
-          <t>Bajo pero relevante</t>
+          <t>Volumen medio</t>
         </is>
       </c>
     </row>
@@ -6862,27 +6862,27 @@
       </c>
       <c r="B213" s="3" t="inlineStr">
         <is>
-          <t>lugares para cenar conos de boneless para bajar la cruda en el istmo</t>
-        </is>
-      </c>
-      <c r="C213" s="7" t="inlineStr">
-        <is>
-          <t>MEDIO-BAJO</t>
+          <t>que hacer por la tarde en ixtepec</t>
+        </is>
+      </c>
+      <c r="C213" s="6" t="inlineStr">
+        <is>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>10-20</t>
+          <t>20-50</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>Informativa</t>
+          <t>Busqueda</t>
         </is>
       </c>
       <c r="F213" s="3" t="inlineStr">
         <is>
-          <t>Bajo pero relevante</t>
+          <t>Volumen medio</t>
         </is>
       </c>
     </row>
@@ -6892,27 +6892,27 @@
       </c>
       <c r="B214" s="3" t="inlineStr">
         <is>
-          <t>mejores alitas del istmo de tehuantepec</t>
-        </is>
-      </c>
-      <c r="C214" s="7" t="inlineStr">
-        <is>
-          <t>MEDIO-BAJO</t>
+          <t>restaurantes de alitas de madrugada en el istmo</t>
+        </is>
+      </c>
+      <c r="C214" s="6" t="inlineStr">
+        <is>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>10-20</t>
+          <t>20-50</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>Comparativa</t>
+          <t>Informativa</t>
         </is>
       </c>
       <c r="F214" s="3" t="inlineStr">
         <is>
-          <t>Bajo pero relevante</t>
+          <t>Volumen medio</t>
         </is>
       </c>
     </row>
@@ -6922,27 +6922,27 @@
       </c>
       <c r="B215" s="3" t="inlineStr">
         <is>
-          <t>mejores lugares para comer botanas cerca del parque ixtepec</t>
-        </is>
-      </c>
-      <c r="C215" s="7" t="inlineStr">
-        <is>
-          <t>MEDIO-BAJO</t>
+          <t>restaurantes de cenas baratas cerca del parque ixtepec</t>
+        </is>
+      </c>
+      <c r="C215" s="6" t="inlineStr">
+        <is>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>10-20</t>
+          <t>20-50</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>Comparativa</t>
+          <t>Informativa</t>
         </is>
       </c>
       <c r="F215" s="3" t="inlineStr">
         <is>
-          <t>Bajo pero relevante</t>
+          <t>Volumen medio</t>
         </is>
       </c>
     </row>
@@ -6952,27 +6952,27 @@
       </c>
       <c r="B216" s="3" t="inlineStr">
         <is>
-          <t>mejores lugares para comer botanas de madrugada en el istmo</t>
-        </is>
-      </c>
-      <c r="C216" s="7" t="inlineStr">
-        <is>
-          <t>MEDIO-BAJO</t>
+          <t>restaurantes de frappes frios para bajar la cruda en el istmo</t>
+        </is>
+      </c>
+      <c r="C216" s="6" t="inlineStr">
+        <is>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>10-20</t>
+          <t>20-50</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>Comparativa</t>
+          <t>Informativa</t>
         </is>
       </c>
       <c r="F216" s="3" t="inlineStr">
         <is>
-          <t>Bajo pero relevante</t>
+          <t>Volumen medio</t>
         </is>
       </c>
     </row>
@@ -6982,17 +6982,17 @@
       </c>
       <c r="B217" s="3" t="inlineStr">
         <is>
-          <t>papas con queso y tocino en ixtepec</t>
-        </is>
-      </c>
-      <c r="C217" s="7" t="inlineStr">
-        <is>
-          <t>MEDIO-BAJO</t>
+          <t>restaurantes de snacks en el istmo</t>
+        </is>
+      </c>
+      <c r="C217" s="6" t="inlineStr">
+        <is>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>10-20</t>
+          <t>20-50</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F217" s="3" t="inlineStr">
         <is>
-          <t>Bajo pero relevante</t>
+          <t>Volumen medio</t>
         </is>
       </c>
     </row>
@@ -7012,7 +7012,7 @@
       </c>
       <c r="B218" s="3" t="inlineStr">
         <is>
-          <t>precio de boneless en el istmo de tehuantepec</t>
+          <t>alitas muy picosas del istmo</t>
         </is>
       </c>
       <c r="C218" s="7" t="inlineStr">
@@ -7027,7 +7027,7 @@
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>Transaccional</t>
+          <t>Informativa</t>
         </is>
       </c>
       <c r="F218" s="3" t="inlineStr">
@@ -7042,7 +7042,7 @@
       </c>
       <c r="B219" s="3" t="inlineStr">
         <is>
-          <t>promociones de papas con queso cerca del parque ixtepec</t>
+          <t>antojos alitas bbq para bajar la cruda en el istmo</t>
         </is>
       </c>
       <c r="C219" s="7" t="inlineStr">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>Transaccional</t>
+          <t>Informativa</t>
         </is>
       </c>
       <c r="F219" s="3" t="inlineStr">
@@ -7072,17 +7072,17 @@
       </c>
       <c r="B220" s="3" t="inlineStr">
         <is>
-          <t>antojos alitas de madrugada en el istmo</t>
-        </is>
-      </c>
-      <c r="C220" s="8" t="inlineStr">
-        <is>
-          <t>BAJO</t>
+          <t>antojos alitas picosas cerca del parque ixtepec</t>
+        </is>
+      </c>
+      <c r="C220" s="7" t="inlineStr">
+        <is>
+          <t>MEDIO-BAJO</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>0-10</t>
+          <t>10-20</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
@@ -7092,7 +7092,7 @@
       </c>
       <c r="F220" s="3" t="inlineStr">
         <is>
-          <t>Long-tail alta conversion</t>
+          <t>Bajo pero relevante</t>
         </is>
       </c>
     </row>
@@ -7102,17 +7102,17 @@
       </c>
       <c r="B221" s="3" t="inlineStr">
         <is>
-          <t>antojos alitas para bajar la cruda en el istmo</t>
-        </is>
-      </c>
-      <c r="C221" s="8" t="inlineStr">
-        <is>
-          <t>BAJO</t>
+          <t>antojos alitas picosas de madrugada en el istmo</t>
+        </is>
+      </c>
+      <c r="C221" s="7" t="inlineStr">
+        <is>
+          <t>MEDIO-BAJO</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>0-10</t>
+          <t>10-20</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="F221" s="3" t="inlineStr">
         <is>
-          <t>Long-tail alta conversion</t>
+          <t>Bajo pero relevante</t>
         </is>
       </c>
     </row>
@@ -7132,17 +7132,17 @@
       </c>
       <c r="B222" s="3" t="inlineStr">
         <is>
-          <t>antojos botanas en el istmo de tehuantepec</t>
-        </is>
-      </c>
-      <c r="C222" s="8" t="inlineStr">
-        <is>
-          <t>BAJO</t>
+          <t>antojos boneless de madrugada en el istmo</t>
+        </is>
+      </c>
+      <c r="C222" s="7" t="inlineStr">
+        <is>
+          <t>MEDIO-BAJO</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>0-10</t>
+          <t>10-20</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
@@ -7152,7 +7152,7 @@
       </c>
       <c r="F222" s="3" t="inlineStr">
         <is>
-          <t>Long-tail alta conversion</t>
+          <t>Bajo pero relevante</t>
         </is>
       </c>
     </row>
@@ -7162,17 +7162,17 @@
       </c>
       <c r="B223" s="3" t="inlineStr">
         <is>
-          <t>antojos botanas para bajar la cruda en el istmo</t>
-        </is>
-      </c>
-      <c r="C223" s="8" t="inlineStr">
-        <is>
-          <t>BAJO</t>
+          <t>antojos comida para llevar en la noche en ixtepec</t>
+        </is>
+      </c>
+      <c r="C223" s="7" t="inlineStr">
+        <is>
+          <t>MEDIO-BAJO</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>0-10</t>
+          <t>10-20</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
@@ -7182,7 +7182,7 @@
       </c>
       <c r="F223" s="3" t="inlineStr">
         <is>
-          <t>Long-tail alta conversion</t>
+          <t>Bajo pero relevante</t>
         </is>
       </c>
     </row>
@@ -7192,17 +7192,17 @@
       </c>
       <c r="B224" s="3" t="inlineStr">
         <is>
-          <t>comida barata en el istmo de tehuantepec</t>
-        </is>
-      </c>
-      <c r="C224" s="8" t="inlineStr">
-        <is>
-          <t>BAJO</t>
+          <t>antojos papas a la francesa en la noche en ixtepec</t>
+        </is>
+      </c>
+      <c r="C224" s="7" t="inlineStr">
+        <is>
+          <t>MEDIO-BAJO</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>0-10</t>
+          <t>10-20</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="F224" s="3" t="inlineStr">
         <is>
-          <t>Long-tail alta conversion</t>
+          <t>Bajo pero relevante</t>
         </is>
       </c>
     </row>
@@ -7222,27 +7222,27 @@
       </c>
       <c r="B225" s="3" t="inlineStr">
         <is>
-          <t>donde comprar botanas cerca del parque ixtepec</t>
-        </is>
-      </c>
-      <c r="C225" s="8" t="inlineStr">
-        <is>
-          <t>BAJO</t>
+          <t>bebidas para el calor en ixtepec</t>
+        </is>
+      </c>
+      <c r="C225" s="7" t="inlineStr">
+        <is>
+          <t>MEDIO-BAJO</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>0-10</t>
+          <t>10-20</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>Busqueda</t>
+          <t>Informativa</t>
         </is>
       </c>
       <c r="F225" s="3" t="inlineStr">
         <is>
-          <t>Long-tail alta conversion</t>
+          <t>Bajo pero relevante</t>
         </is>
       </c>
     </row>
@@ -7252,27 +7252,27 @@
       </c>
       <c r="B226" s="3" t="inlineStr">
         <is>
-          <t>donde pedir botanas en el istmo de tehuantepec</t>
-        </is>
-      </c>
-      <c r="C226" s="8" t="inlineStr">
-        <is>
-          <t>BAJO</t>
+          <t>comida para jovenes en el istmo</t>
+        </is>
+      </c>
+      <c r="C226" s="7" t="inlineStr">
+        <is>
+          <t>MEDIO-BAJO</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>0-10</t>
+          <t>10-20</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>Busqueda</t>
+          <t>Informativa</t>
         </is>
       </c>
       <c r="F226" s="3" t="inlineStr">
         <is>
-          <t>Long-tail alta conversion</t>
+          <t>Bajo pero relevante</t>
         </is>
       </c>
     </row>
@@ -7282,27 +7282,27 @@
       </c>
       <c r="B227" s="3" t="inlineStr">
         <is>
-          <t>donde pedir cenas baratas en la noche en ixtepec</t>
-        </is>
-      </c>
-      <c r="C227" s="8" t="inlineStr">
-        <is>
-          <t>BAJO</t>
+          <t>comida para reuniones en el istmo</t>
+        </is>
+      </c>
+      <c r="C227" s="7" t="inlineStr">
+        <is>
+          <t>MEDIO-BAJO</t>
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>0-10</t>
+          <t>10-20</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>Busqueda</t>
+          <t>Informativa</t>
         </is>
       </c>
       <c r="F227" s="3" t="inlineStr">
         <is>
-          <t>Long-tail alta conversion</t>
+          <t>Bajo pero relevante</t>
         </is>
       </c>
     </row>
@@ -7312,27 +7312,27 @@
       </c>
       <c r="B228" s="3" t="inlineStr">
         <is>
-          <t>donde pedir papas con queso para bajar la cruda en el istmo</t>
-        </is>
-      </c>
-      <c r="C228" s="8" t="inlineStr">
-        <is>
-          <t>BAJO</t>
+          <t>comida rapida loaded fries cerca del parque ixtepec</t>
+        </is>
+      </c>
+      <c r="C228" s="7" t="inlineStr">
+        <is>
+          <t>MEDIO-BAJO</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>0-10</t>
+          <t>10-20</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>Busqueda</t>
+          <t>Informativa</t>
         </is>
       </c>
       <c r="F228" s="3" t="inlineStr">
         <is>
-          <t>Long-tail alta conversion</t>
+          <t>Bajo pero relevante</t>
         </is>
       </c>
     </row>
@@ -7342,27 +7342,27 @@
       </c>
       <c r="B229" s="3" t="inlineStr">
         <is>
-          <t>donde pedir postres en la noche en ixtepec</t>
-        </is>
-      </c>
-      <c r="C229" s="8" t="inlineStr">
-        <is>
-          <t>BAJO</t>
+          <t>comida rapida loaded fries en el istmo de tehuantepec</t>
+        </is>
+      </c>
+      <c r="C229" s="7" t="inlineStr">
+        <is>
+          <t>MEDIO-BAJO</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>0-10</t>
+          <t>10-20</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>Busqueda</t>
+          <t>Informativa</t>
         </is>
       </c>
       <c r="F229" s="3" t="inlineStr">
         <is>
-          <t>Long-tail alta conversion</t>
+          <t>Bajo pero relevante</t>
         </is>
       </c>
     </row>
@@ -7372,17 +7372,17 @@
       </c>
       <c r="B230" s="3" t="inlineStr">
         <is>
-          <t>donde venden cenas baratas en ciudad ixtepec</t>
-        </is>
-      </c>
-      <c r="C230" s="8" t="inlineStr">
-        <is>
-          <t>BAJO</t>
+          <t>donde celebrar cumplea±os en ixtepec</t>
+        </is>
+      </c>
+      <c r="C230" s="7" t="inlineStr">
+        <is>
+          <t>MEDIO-BAJO</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>0-10</t>
+          <t>10-20</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
@@ -7392,7 +7392,7 @@
       </c>
       <c r="F230" s="3" t="inlineStr">
         <is>
-          <t>Long-tail alta conversion</t>
+          <t>Bajo pero relevante</t>
         </is>
       </c>
     </row>
@@ -7402,17 +7402,17 @@
       </c>
       <c r="B231" s="3" t="inlineStr">
         <is>
-          <t>donde venden snacks en ciudad ixtepec</t>
-        </is>
-      </c>
-      <c r="C231" s="8" t="inlineStr">
-        <is>
-          <t>BAJO</t>
+          <t>donde comer botanas cerca del parque ixtepec</t>
+        </is>
+      </c>
+      <c r="C231" s="7" t="inlineStr">
+        <is>
+          <t>MEDIO-BAJO</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>0-10</t>
+          <t>10-20</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="F231" s="3" t="inlineStr">
         <is>
-          <t>Long-tail alta conversion</t>
+          <t>Bajo pero relevante</t>
         </is>
       </c>
     </row>
@@ -7432,27 +7432,27 @@
       </c>
       <c r="B232" s="3" t="inlineStr">
         <is>
-          <t>las mejores botanas en la noche en ixtepec</t>
-        </is>
-      </c>
-      <c r="C232" s="8" t="inlineStr">
-        <is>
-          <t>BAJO</t>
+          <t>donde pedir alitas bbq de madrugada en el istmo</t>
+        </is>
+      </c>
+      <c r="C232" s="7" t="inlineStr">
+        <is>
+          <t>MEDIO-BAJO</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>0-10</t>
+          <t>10-20</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>Comparativa</t>
+          <t>Busqueda</t>
         </is>
       </c>
       <c r="F232" s="3" t="inlineStr">
         <is>
-          <t>Long-tail alta conversion</t>
+          <t>Bajo pero relevante</t>
         </is>
       </c>
     </row>
@@ -7462,27 +7462,27 @@
       </c>
       <c r="B233" s="3" t="inlineStr">
         <is>
-          <t>lugares chidos para salir con amigos en el istmo</t>
-        </is>
-      </c>
-      <c r="C233" s="8" t="inlineStr">
-        <is>
-          <t>BAJO</t>
+          <t>donde pedir frappes de madrugada en el istmo</t>
+        </is>
+      </c>
+      <c r="C233" s="7" t="inlineStr">
+        <is>
+          <t>MEDIO-BAJO</t>
         </is>
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>0-10</t>
+          <t>10-20</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>Informativa</t>
+          <t>Busqueda</t>
         </is>
       </c>
       <c r="F233" s="3" t="inlineStr">
         <is>
-          <t>Long-tail alta conversion</t>
+          <t>Bajo pero relevante</t>
         </is>
       </c>
     </row>
@@ -7492,27 +7492,27 @@
       </c>
       <c r="B234" s="3" t="inlineStr">
         <is>
-          <t>lugares para cenar cenas baratas cerca del parque ixtepec</t>
-        </is>
-      </c>
-      <c r="C234" s="8" t="inlineStr">
-        <is>
-          <t>BAJO</t>
+          <t>donde pedir hamburguesas para bajar la cruda en el istmo</t>
+        </is>
+      </c>
+      <c r="C234" s="7" t="inlineStr">
+        <is>
+          <t>MEDIO-BAJO</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>0-10</t>
+          <t>10-20</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>Informativa</t>
+          <t>Busqueda</t>
         </is>
       </c>
       <c r="F234" s="3" t="inlineStr">
         <is>
-          <t>Long-tail alta conversion</t>
+          <t>Bajo pero relevante</t>
         </is>
       </c>
     </row>
@@ -7522,27 +7522,27 @@
       </c>
       <c r="B235" s="3" t="inlineStr">
         <is>
-          <t>precio de alitas picosas de madrugada en el istmo</t>
-        </is>
-      </c>
-      <c r="C235" s="8" t="inlineStr">
-        <is>
-          <t>BAJO</t>
+          <t>donde pedir papas a la francesa en el istmo de tehuantepec</t>
+        </is>
+      </c>
+      <c r="C235" s="7" t="inlineStr">
+        <is>
+          <t>MEDIO-BAJO</t>
         </is>
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>0-10</t>
+          <t>10-20</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>Transaccional</t>
+          <t>Busqueda</t>
         </is>
       </c>
       <c r="F235" s="3" t="inlineStr">
         <is>
-          <t>Long-tail alta conversion</t>
+          <t>Bajo pero relevante</t>
         </is>
       </c>
     </row>
@@ -7552,27 +7552,27 @@
       </c>
       <c r="B236" s="3" t="inlineStr">
         <is>
-          <t>precio de botanas en el istmo</t>
-        </is>
-      </c>
-      <c r="C236" s="8" t="inlineStr">
-        <is>
-          <t>BAJO</t>
+          <t>donde pedir postres a domicilio en ixtepec</t>
+        </is>
+      </c>
+      <c r="C236" s="7" t="inlineStr">
+        <is>
+          <t>MEDIO-BAJO</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>0-10</t>
+          <t>10-20</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>Transaccional</t>
+          <t>Busqueda</t>
         </is>
       </c>
       <c r="F236" s="3" t="inlineStr">
         <is>
-          <t>Long-tail alta conversion</t>
+          <t>Bajo pero relevante</t>
         </is>
       </c>
     </row>
@@ -7582,27 +7582,27 @@
       </c>
       <c r="B237" s="3" t="inlineStr">
         <is>
-          <t>precio de comida para llevar cerca del parque ixtepec</t>
-        </is>
-      </c>
-      <c r="C237" s="8" t="inlineStr">
-        <is>
-          <t>BAJO</t>
+          <t>donde venden alitas picosas en la noche en ixtepec</t>
+        </is>
+      </c>
+      <c r="C237" s="7" t="inlineStr">
+        <is>
+          <t>MEDIO-BAJO</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>0-10</t>
+          <t>10-20</t>
         </is>
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>Transaccional</t>
+          <t>Busqueda</t>
         </is>
       </c>
       <c r="F237" s="3" t="inlineStr">
         <is>
-          <t>Long-tail alta conversion</t>
+          <t>Bajo pero relevante</t>
         </is>
       </c>
     </row>
@@ -7612,27 +7612,27 @@
       </c>
       <c r="B238" s="3" t="inlineStr">
         <is>
-          <t>precio de conos de boneless en el istmo de tehuantepec</t>
-        </is>
-      </c>
-      <c r="C238" s="8" t="inlineStr">
-        <is>
-          <t>BAJO</t>
+          <t>donde venden frappes frios en la noche en ixtepec</t>
+        </is>
+      </c>
+      <c r="C238" s="7" t="inlineStr">
+        <is>
+          <t>MEDIO-BAJO</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>0-10</t>
+          <t>10-20</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>Transaccional</t>
+          <t>Busqueda</t>
         </is>
       </c>
       <c r="F238" s="3" t="inlineStr">
         <is>
-          <t>Long-tail alta conversion</t>
+          <t>Bajo pero relevante</t>
         </is>
       </c>
     </row>
@@ -7642,27 +7642,27 @@
       </c>
       <c r="B239" s="3" t="inlineStr">
         <is>
-          <t>precio de papas a la francesa cerca del parque ixtepec</t>
-        </is>
-      </c>
-      <c r="C239" s="8" t="inlineStr">
-        <is>
-          <t>BAJO</t>
+          <t>donde ver el partido de futbol en el istmo</t>
+        </is>
+      </c>
+      <c r="C239" s="7" t="inlineStr">
+        <is>
+          <t>MEDIO-BAJO</t>
         </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>0-10</t>
+          <t>10-20</t>
         </is>
       </c>
       <c r="E239" s="2" t="inlineStr">
         <is>
-          <t>Transaccional</t>
+          <t>Busqueda</t>
         </is>
       </c>
       <c r="F239" s="3" t="inlineStr">
         <is>
-          <t>Long-tail alta conversion</t>
+          <t>Bajo pero relevante</t>
         </is>
       </c>
     </row>
@@ -7672,27 +7672,27 @@
       </c>
       <c r="B240" s="3" t="inlineStr">
         <is>
-          <t>precio de papas a la francesa en ciudad ixtepec</t>
-        </is>
-      </c>
-      <c r="C240" s="8" t="inlineStr">
-        <is>
-          <t>BAJO</t>
+          <t>hamburguesa de arrachera en el istmo</t>
+        </is>
+      </c>
+      <c r="C240" s="7" t="inlineStr">
+        <is>
+          <t>MEDIO-BAJO</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>0-10</t>
+          <t>10-20</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>Transaccional</t>
+          <t>Informativa</t>
         </is>
       </c>
       <c r="F240" s="3" t="inlineStr">
         <is>
-          <t>Long-tail alta conversion</t>
+          <t>Bajo pero relevante</t>
         </is>
       </c>
     </row>
@@ -7702,27 +7702,27 @@
       </c>
       <c r="B241" s="3" t="inlineStr">
         <is>
-          <t>precio de papas a la francesa en el istmo de tehuantepec</t>
-        </is>
-      </c>
-      <c r="C241" s="8" t="inlineStr">
-        <is>
-          <t>BAJO</t>
+          <t>hamburguesa de arrachera en ixtepec</t>
+        </is>
+      </c>
+      <c r="C241" s="7" t="inlineStr">
+        <is>
+          <t>MEDIO-BAJO</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>0-10</t>
+          <t>10-20</t>
         </is>
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>Transaccional</t>
+          <t>Informativa</t>
         </is>
       </c>
       <c r="F241" s="3" t="inlineStr">
         <is>
-          <t>Long-tail alta conversion</t>
+          <t>Bajo pero relevante</t>
         </is>
       </c>
     </row>
@@ -7732,27 +7732,27 @@
       </c>
       <c r="B242" s="3" t="inlineStr">
         <is>
-          <t>precio de snacks de madrugada en el istmo</t>
-        </is>
-      </c>
-      <c r="C242" s="8" t="inlineStr">
-        <is>
-          <t>BAJO</t>
+          <t>las mejores frappes de madrugada en el istmo</t>
+        </is>
+      </c>
+      <c r="C242" s="7" t="inlineStr">
+        <is>
+          <t>MEDIO-BAJO</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>0-10</t>
+          <t>10-20</t>
         </is>
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>Transaccional</t>
+          <t>Comparativa</t>
         </is>
       </c>
       <c r="F242" s="3" t="inlineStr">
         <is>
-          <t>Long-tail alta conversion</t>
+          <t>Bajo pero relevante</t>
         </is>
       </c>
     </row>
@@ -7762,25 +7762,1435 @@
       </c>
       <c r="B243" s="3" t="inlineStr">
         <is>
+          <t>las mejores hamburguesas para bajar la cruda en el istmo</t>
+        </is>
+      </c>
+      <c r="C243" s="7" t="inlineStr">
+        <is>
+          <t>MEDIO-BAJO</t>
+        </is>
+      </c>
+      <c r="D243" s="2" t="inlineStr">
+        <is>
+          <t>10-20</t>
+        </is>
+      </c>
+      <c r="E243" s="2" t="inlineStr">
+        <is>
+          <t>Comparativa</t>
+        </is>
+      </c>
+      <c r="F243" s="3" t="inlineStr">
+        <is>
+          <t>Bajo pero relevante</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="n">
+        <v>243</v>
+      </c>
+      <c r="B244" s="3" t="inlineStr">
+        <is>
+          <t>lugares para cenar alitas bbq para bajar la cruda en el istmo</t>
+        </is>
+      </c>
+      <c r="C244" s="7" t="inlineStr">
+        <is>
+          <t>MEDIO-BAJO</t>
+        </is>
+      </c>
+      <c r="D244" s="2" t="inlineStr">
+        <is>
+          <t>10-20</t>
+        </is>
+      </c>
+      <c r="E244" s="2" t="inlineStr">
+        <is>
+          <t>Informativa</t>
+        </is>
+      </c>
+      <c r="F244" s="3" t="inlineStr">
+        <is>
+          <t>Bajo pero relevante</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="n">
+        <v>244</v>
+      </c>
+      <c r="B245" s="3" t="inlineStr">
+        <is>
+          <t>lugares para cenar alitas picosas en la noche en ixtepec</t>
+        </is>
+      </c>
+      <c r="C245" s="7" t="inlineStr">
+        <is>
+          <t>MEDIO-BAJO</t>
+        </is>
+      </c>
+      <c r="D245" s="2" t="inlineStr">
+        <is>
+          <t>10-20</t>
+        </is>
+      </c>
+      <c r="E245" s="2" t="inlineStr">
+        <is>
+          <t>Informativa</t>
+        </is>
+      </c>
+      <c r="F245" s="3" t="inlineStr">
+        <is>
+          <t>Bajo pero relevante</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="B246" s="3" t="inlineStr">
+        <is>
+          <t>mejores alitas del istmo de tehuantepec</t>
+        </is>
+      </c>
+      <c r="C246" s="7" t="inlineStr">
+        <is>
+          <t>MEDIO-BAJO</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
+        <is>
+          <t>10-20</t>
+        </is>
+      </c>
+      <c r="E246" s="2" t="inlineStr">
+        <is>
+          <t>Comparativa</t>
+        </is>
+      </c>
+      <c r="F246" s="3" t="inlineStr">
+        <is>
+          <t>Bajo pero relevante</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="n">
+        <v>246</v>
+      </c>
+      <c r="B247" s="3" t="inlineStr">
+        <is>
+          <t>precio de comida para llevar en ixtepec</t>
+        </is>
+      </c>
+      <c r="C247" s="7" t="inlineStr">
+        <is>
+          <t>MEDIO-BAJO</t>
+        </is>
+      </c>
+      <c r="D247" s="2" t="inlineStr">
+        <is>
+          <t>10-20</t>
+        </is>
+      </c>
+      <c r="E247" s="2" t="inlineStr">
+        <is>
+          <t>Transaccional</t>
+        </is>
+      </c>
+      <c r="F247" s="3" t="inlineStr">
+        <is>
+          <t>Bajo pero relevante</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="n">
+        <v>247</v>
+      </c>
+      <c r="B248" s="3" t="inlineStr">
+        <is>
+          <t>promociones de loaded fries en el istmo</t>
+        </is>
+      </c>
+      <c r="C248" s="7" t="inlineStr">
+        <is>
+          <t>MEDIO-BAJO</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="inlineStr">
+        <is>
+          <t>10-20</t>
+        </is>
+      </c>
+      <c r="E248" s="2" t="inlineStr">
+        <is>
+          <t>Transaccional</t>
+        </is>
+      </c>
+      <c r="F248" s="3" t="inlineStr">
+        <is>
+          <t>Bajo pero relevante</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="n">
+        <v>248</v>
+      </c>
+      <c r="B249" s="3" t="inlineStr">
+        <is>
+          <t>que comer en el istmo</t>
+        </is>
+      </c>
+      <c r="C249" s="7" t="inlineStr">
+        <is>
+          <t>MEDIO-BAJO</t>
+        </is>
+      </c>
+      <c r="D249" s="2" t="inlineStr">
+        <is>
+          <t>10-20</t>
+        </is>
+      </c>
+      <c r="E249" s="2" t="inlineStr">
+        <is>
+          <t>Busqueda</t>
+        </is>
+      </c>
+      <c r="F249" s="3" t="inlineStr">
+        <is>
+          <t>Bajo pero relevante</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="n">
+        <v>249</v>
+      </c>
+      <c r="B250" s="3" t="inlineStr">
+        <is>
+          <t>restaurante para jovenes en el istmo</t>
+        </is>
+      </c>
+      <c r="C250" s="7" t="inlineStr">
+        <is>
+          <t>MEDIO-BAJO</t>
+        </is>
+      </c>
+      <c r="D250" s="2" t="inlineStr">
+        <is>
+          <t>10-20</t>
+        </is>
+      </c>
+      <c r="E250" s="2" t="inlineStr">
+        <is>
+          <t>Informativa</t>
+        </is>
+      </c>
+      <c r="F250" s="3" t="inlineStr">
+        <is>
+          <t>Bajo pero relevante</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="n">
+        <v>250</v>
+      </c>
+      <c r="B251" s="3" t="inlineStr">
+        <is>
+          <t>restaurante para jovenes en ixtepec</t>
+        </is>
+      </c>
+      <c r="C251" s="7" t="inlineStr">
+        <is>
+          <t>MEDIO-BAJO</t>
+        </is>
+      </c>
+      <c r="D251" s="2" t="inlineStr">
+        <is>
+          <t>10-20</t>
+        </is>
+      </c>
+      <c r="E251" s="2" t="inlineStr">
+        <is>
+          <t>Informativa</t>
+        </is>
+      </c>
+      <c r="F251" s="3" t="inlineStr">
+        <is>
+          <t>Bajo pero relevante</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="n">
+        <v>251</v>
+      </c>
+      <c r="B252" s="3" t="inlineStr">
+        <is>
+          <t>antojos alitas de madrugada en el istmo</t>
+        </is>
+      </c>
+      <c r="C252" s="8" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="D252" s="2" t="inlineStr">
+        <is>
+          <t>0-10</t>
+        </is>
+      </c>
+      <c r="E252" s="2" t="inlineStr">
+        <is>
+          <t>Informativa</t>
+        </is>
+      </c>
+      <c r="F252" s="3" t="inlineStr">
+        <is>
+          <t>Long-tail alta conversion</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="n">
+        <v>252</v>
+      </c>
+      <c r="B253" s="3" t="inlineStr">
+        <is>
+          <t>antojos alitas para bajar la cruda en el istmo</t>
+        </is>
+      </c>
+      <c r="C253" s="8" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="D253" s="2" t="inlineStr">
+        <is>
+          <t>0-10</t>
+        </is>
+      </c>
+      <c r="E253" s="2" t="inlineStr">
+        <is>
+          <t>Informativa</t>
+        </is>
+      </c>
+      <c r="F253" s="3" t="inlineStr">
+        <is>
+          <t>Long-tail alta conversion</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="n">
+        <v>253</v>
+      </c>
+      <c r="B254" s="3" t="inlineStr">
+        <is>
+          <t>antojos botanas en el istmo de tehuantepec</t>
+        </is>
+      </c>
+      <c r="C254" s="8" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="D254" s="2" t="inlineStr">
+        <is>
+          <t>0-10</t>
+        </is>
+      </c>
+      <c r="E254" s="2" t="inlineStr">
+        <is>
+          <t>Informativa</t>
+        </is>
+      </c>
+      <c r="F254" s="3" t="inlineStr">
+        <is>
+          <t>Long-tail alta conversion</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="n">
+        <v>254</v>
+      </c>
+      <c r="B255" s="3" t="inlineStr">
+        <is>
+          <t>antojos botanas para bajar la cruda en el istmo</t>
+        </is>
+      </c>
+      <c r="C255" s="8" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="D255" s="2" t="inlineStr">
+        <is>
+          <t>0-10</t>
+        </is>
+      </c>
+      <c r="E255" s="2" t="inlineStr">
+        <is>
+          <t>Informativa</t>
+        </is>
+      </c>
+      <c r="F255" s="3" t="inlineStr">
+        <is>
+          <t>Long-tail alta conversion</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="n">
+        <v>255</v>
+      </c>
+      <c r="B256" s="3" t="inlineStr">
+        <is>
+          <t>antojos papas a la francesa cerca del parque ixtepec</t>
+        </is>
+      </c>
+      <c r="C256" s="8" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="D256" s="2" t="inlineStr">
+        <is>
+          <t>0-10</t>
+        </is>
+      </c>
+      <c r="E256" s="2" t="inlineStr">
+        <is>
+          <t>Informativa</t>
+        </is>
+      </c>
+      <c r="F256" s="3" t="inlineStr">
+        <is>
+          <t>Long-tail alta conversion</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="n">
+        <v>256</v>
+      </c>
+      <c r="B257" s="3" t="inlineStr">
+        <is>
+          <t>antojos papas a la francesa para bajar la cruda en el istmo</t>
+        </is>
+      </c>
+      <c r="C257" s="8" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="D257" s="2" t="inlineStr">
+        <is>
+          <t>0-10</t>
+        </is>
+      </c>
+      <c r="E257" s="2" t="inlineStr">
+        <is>
+          <t>Informativa</t>
+        </is>
+      </c>
+      <c r="F257" s="3" t="inlineStr">
+        <is>
+          <t>Long-tail alta conversion</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="n">
+        <v>257</v>
+      </c>
+      <c r="B258" s="3" t="inlineStr">
+        <is>
+          <t>cenadurias con papas a la francesa para bajar la cruda en el istmo</t>
+        </is>
+      </c>
+      <c r="C258" s="8" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="D258" s="2" t="inlineStr">
+        <is>
+          <t>0-10</t>
+        </is>
+      </c>
+      <c r="E258" s="2" t="inlineStr">
+        <is>
+          <t>Informativa</t>
+        </is>
+      </c>
+      <c r="F258" s="3" t="inlineStr">
+        <is>
+          <t>Long-tail alta conversion</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="n">
+        <v>258</v>
+      </c>
+      <c r="B259" s="3" t="inlineStr">
+        <is>
+          <t>comida barata en el istmo de tehuantepec</t>
+        </is>
+      </c>
+      <c r="C259" s="8" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="D259" s="2" t="inlineStr">
+        <is>
+          <t>0-10</t>
+        </is>
+      </c>
+      <c r="E259" s="2" t="inlineStr">
+        <is>
+          <t>Informativa</t>
+        </is>
+      </c>
+      <c r="F259" s="3" t="inlineStr">
+        <is>
+          <t>Long-tail alta conversion</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="n">
+        <v>259</v>
+      </c>
+      <c r="B260" s="3" t="inlineStr">
+        <is>
+          <t>donde comer botanas para bajar la cruda en el istmo</t>
+        </is>
+      </c>
+      <c r="C260" s="8" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="D260" s="2" t="inlineStr">
+        <is>
+          <t>0-10</t>
+        </is>
+      </c>
+      <c r="E260" s="2" t="inlineStr">
+        <is>
+          <t>Busqueda</t>
+        </is>
+      </c>
+      <c r="F260" s="3" t="inlineStr">
+        <is>
+          <t>Long-tail alta conversion</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="n">
+        <v>260</v>
+      </c>
+      <c r="B261" s="3" t="inlineStr">
+        <is>
+          <t>donde comer loaded fries para bajar la cruda en el istmo</t>
+        </is>
+      </c>
+      <c r="C261" s="8" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="D261" s="2" t="inlineStr">
+        <is>
+          <t>0-10</t>
+        </is>
+      </c>
+      <c r="E261" s="2" t="inlineStr">
+        <is>
+          <t>Busqueda</t>
+        </is>
+      </c>
+      <c r="F261" s="3" t="inlineStr">
+        <is>
+          <t>Long-tail alta conversion</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="n">
+        <v>261</v>
+      </c>
+      <c r="B262" s="3" t="inlineStr">
+        <is>
+          <t>donde comer snacks para bajar la cruda en el istmo</t>
+        </is>
+      </c>
+      <c r="C262" s="8" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="D262" s="2" t="inlineStr">
+        <is>
+          <t>0-10</t>
+        </is>
+      </c>
+      <c r="E262" s="2" t="inlineStr">
+        <is>
+          <t>Busqueda</t>
+        </is>
+      </c>
+      <c r="F262" s="3" t="inlineStr">
+        <is>
+          <t>Long-tail alta conversion</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="n">
+        <v>262</v>
+      </c>
+      <c r="B263" s="3" t="inlineStr">
+        <is>
+          <t>donde comprar boneless para bajar la cruda en el istmo</t>
+        </is>
+      </c>
+      <c r="C263" s="8" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="D263" s="2" t="inlineStr">
+        <is>
+          <t>0-10</t>
+        </is>
+      </c>
+      <c r="E263" s="2" t="inlineStr">
+        <is>
+          <t>Busqueda</t>
+        </is>
+      </c>
+      <c r="F263" s="3" t="inlineStr">
+        <is>
+          <t>Long-tail alta conversion</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="n">
+        <v>263</v>
+      </c>
+      <c r="B264" s="3" t="inlineStr">
+        <is>
+          <t>donde comprar botanas cerca del parque ixtepec</t>
+        </is>
+      </c>
+      <c r="C264" s="8" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="D264" s="2" t="inlineStr">
+        <is>
+          <t>0-10</t>
+        </is>
+      </c>
+      <c r="E264" s="2" t="inlineStr">
+        <is>
+          <t>Busqueda</t>
+        </is>
+      </c>
+      <c r="F264" s="3" t="inlineStr">
+        <is>
+          <t>Long-tail alta conversion</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="n">
+        <v>264</v>
+      </c>
+      <c r="B265" s="3" t="inlineStr">
+        <is>
+          <t>donde pedir botanas en el istmo de tehuantepec</t>
+        </is>
+      </c>
+      <c r="C265" s="8" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="D265" s="2" t="inlineStr">
+        <is>
+          <t>0-10</t>
+        </is>
+      </c>
+      <c r="E265" s="2" t="inlineStr">
+        <is>
+          <t>Busqueda</t>
+        </is>
+      </c>
+      <c r="F265" s="3" t="inlineStr">
+        <is>
+          <t>Long-tail alta conversion</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="n">
+        <v>265</v>
+      </c>
+      <c r="B266" s="3" t="inlineStr">
+        <is>
+          <t>donde pedir cenas baratas en la noche en ixtepec</t>
+        </is>
+      </c>
+      <c r="C266" s="8" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="D266" s="2" t="inlineStr">
+        <is>
+          <t>0-10</t>
+        </is>
+      </c>
+      <c r="E266" s="2" t="inlineStr">
+        <is>
+          <t>Busqueda</t>
+        </is>
+      </c>
+      <c r="F266" s="3" t="inlineStr">
+        <is>
+          <t>Long-tail alta conversion</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="n">
+        <v>266</v>
+      </c>
+      <c r="B267" s="3" t="inlineStr">
+        <is>
+          <t>donde pedir comida para llevar cerca del parque ixtepec</t>
+        </is>
+      </c>
+      <c r="C267" s="8" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="D267" s="2" t="inlineStr">
+        <is>
+          <t>0-10</t>
+        </is>
+      </c>
+      <c r="E267" s="2" t="inlineStr">
+        <is>
+          <t>Busqueda</t>
+        </is>
+      </c>
+      <c r="F267" s="3" t="inlineStr">
+        <is>
+          <t>Long-tail alta conversion</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="n">
+        <v>267</v>
+      </c>
+      <c r="B268" s="3" t="inlineStr">
+        <is>
+          <t>donde pedir comida para llevar para bajar la cruda en el istmo</t>
+        </is>
+      </c>
+      <c r="C268" s="8" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="D268" s="2" t="inlineStr">
+        <is>
+          <t>0-10</t>
+        </is>
+      </c>
+      <c r="E268" s="2" t="inlineStr">
+        <is>
+          <t>Busqueda</t>
+        </is>
+      </c>
+      <c r="F268" s="3" t="inlineStr">
+        <is>
+          <t>Long-tail alta conversion</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="n">
+        <v>268</v>
+      </c>
+      <c r="B269" s="3" t="inlineStr">
+        <is>
+          <t>donde pedir papas con queso para bajar la cruda en el istmo</t>
+        </is>
+      </c>
+      <c r="C269" s="8" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="D269" s="2" t="inlineStr">
+        <is>
+          <t>0-10</t>
+        </is>
+      </c>
+      <c r="E269" s="2" t="inlineStr">
+        <is>
+          <t>Busqueda</t>
+        </is>
+      </c>
+      <c r="F269" s="3" t="inlineStr">
+        <is>
+          <t>Long-tail alta conversion</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="n">
+        <v>269</v>
+      </c>
+      <c r="B270" s="3" t="inlineStr">
+        <is>
+          <t>donde pedir postres en la noche en ixtepec</t>
+        </is>
+      </c>
+      <c r="C270" s="8" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="D270" s="2" t="inlineStr">
+        <is>
+          <t>0-10</t>
+        </is>
+      </c>
+      <c r="E270" s="2" t="inlineStr">
+        <is>
+          <t>Busqueda</t>
+        </is>
+      </c>
+      <c r="F270" s="3" t="inlineStr">
+        <is>
+          <t>Long-tail alta conversion</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="n">
+        <v>270</v>
+      </c>
+      <c r="B271" s="3" t="inlineStr">
+        <is>
+          <t>donde venden cenas baratas en ciudad ixtepec</t>
+        </is>
+      </c>
+      <c r="C271" s="8" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="D271" s="2" t="inlineStr">
+        <is>
+          <t>0-10</t>
+        </is>
+      </c>
+      <c r="E271" s="2" t="inlineStr">
+        <is>
+          <t>Busqueda</t>
+        </is>
+      </c>
+      <c r="F271" s="3" t="inlineStr">
+        <is>
+          <t>Long-tail alta conversion</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="n">
+        <v>271</v>
+      </c>
+      <c r="B272" s="3" t="inlineStr">
+        <is>
+          <t>donde venden comida para llevar para bajar la cruda en el istmo</t>
+        </is>
+      </c>
+      <c r="C272" s="8" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="D272" s="2" t="inlineStr">
+        <is>
+          <t>0-10</t>
+        </is>
+      </c>
+      <c r="E272" s="2" t="inlineStr">
+        <is>
+          <t>Busqueda</t>
+        </is>
+      </c>
+      <c r="F272" s="3" t="inlineStr">
+        <is>
+          <t>Long-tail alta conversion</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="n">
+        <v>272</v>
+      </c>
+      <c r="B273" s="3" t="inlineStr">
+        <is>
+          <t>donde venden frappes frios para bajar la cruda en el istmo</t>
+        </is>
+      </c>
+      <c r="C273" s="8" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="D273" s="2" t="inlineStr">
+        <is>
+          <t>0-10</t>
+        </is>
+      </c>
+      <c r="E273" s="2" t="inlineStr">
+        <is>
+          <t>Busqueda</t>
+        </is>
+      </c>
+      <c r="F273" s="3" t="inlineStr">
+        <is>
+          <t>Long-tail alta conversion</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="n">
+        <v>273</v>
+      </c>
+      <c r="B274" s="3" t="inlineStr">
+        <is>
+          <t>donde venden snacks en ciudad ixtepec</t>
+        </is>
+      </c>
+      <c r="C274" s="8" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="D274" s="2" t="inlineStr">
+        <is>
+          <t>0-10</t>
+        </is>
+      </c>
+      <c r="E274" s="2" t="inlineStr">
+        <is>
+          <t>Busqueda</t>
+        </is>
+      </c>
+      <c r="F274" s="3" t="inlineStr">
+        <is>
+          <t>Long-tail alta conversion</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="n">
+        <v>274</v>
+      </c>
+      <c r="B275" s="3" t="inlineStr">
+        <is>
+          <t>las mejores botanas en la noche en ixtepec</t>
+        </is>
+      </c>
+      <c r="C275" s="8" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="D275" s="2" t="inlineStr">
+        <is>
+          <t>0-10</t>
+        </is>
+      </c>
+      <c r="E275" s="2" t="inlineStr">
+        <is>
+          <t>Comparativa</t>
+        </is>
+      </c>
+      <c r="F275" s="3" t="inlineStr">
+        <is>
+          <t>Long-tail alta conversion</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="n">
+        <v>275</v>
+      </c>
+      <c r="B276" s="3" t="inlineStr">
+        <is>
+          <t>las mejores loaded fries en ixtepec</t>
+        </is>
+      </c>
+      <c r="C276" s="8" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="D276" s="2" t="inlineStr">
+        <is>
+          <t>0-10</t>
+        </is>
+      </c>
+      <c r="E276" s="2" t="inlineStr">
+        <is>
+          <t>Comparativa</t>
+        </is>
+      </c>
+      <c r="F276" s="3" t="inlineStr">
+        <is>
+          <t>Long-tail alta conversion</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="n">
+        <v>276</v>
+      </c>
+      <c r="B277" s="3" t="inlineStr">
+        <is>
+          <t>lugares chidos para salir con amigos en el istmo</t>
+        </is>
+      </c>
+      <c r="C277" s="8" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="D277" s="2" t="inlineStr">
+        <is>
+          <t>0-10</t>
+        </is>
+      </c>
+      <c r="E277" s="2" t="inlineStr">
+        <is>
+          <t>Informativa</t>
+        </is>
+      </c>
+      <c r="F277" s="3" t="inlineStr">
+        <is>
+          <t>Long-tail alta conversion</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="n">
+        <v>277</v>
+      </c>
+      <c r="B278" s="3" t="inlineStr">
+        <is>
+          <t>lugares para cenar cenas baratas cerca del parque ixtepec</t>
+        </is>
+      </c>
+      <c r="C278" s="8" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="D278" s="2" t="inlineStr">
+        <is>
+          <t>0-10</t>
+        </is>
+      </c>
+      <c r="E278" s="2" t="inlineStr">
+        <is>
+          <t>Informativa</t>
+        </is>
+      </c>
+      <c r="F278" s="3" t="inlineStr">
+        <is>
+          <t>Long-tail alta conversion</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="n">
+        <v>278</v>
+      </c>
+      <c r="B279" s="3" t="inlineStr">
+        <is>
+          <t>lugares para cenar conos de boneless de madrugada en el istmo</t>
+        </is>
+      </c>
+      <c r="C279" s="8" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="D279" s="2" t="inlineStr">
+        <is>
+          <t>0-10</t>
+        </is>
+      </c>
+      <c r="E279" s="2" t="inlineStr">
+        <is>
+          <t>Informativa</t>
+        </is>
+      </c>
+      <c r="F279" s="3" t="inlineStr">
+        <is>
+          <t>Long-tail alta conversion</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="n">
+        <v>279</v>
+      </c>
+      <c r="B280" s="3" t="inlineStr">
+        <is>
+          <t>lugares para cenar conos de boneless para bajar la cruda en el istmo</t>
+        </is>
+      </c>
+      <c r="C280" s="8" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="D280" s="2" t="inlineStr">
+        <is>
+          <t>0-10</t>
+        </is>
+      </c>
+      <c r="E280" s="2" t="inlineStr">
+        <is>
+          <t>Informativa</t>
+        </is>
+      </c>
+      <c r="F280" s="3" t="inlineStr">
+        <is>
+          <t>Long-tail alta conversion</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="2" t="n">
+        <v>280</v>
+      </c>
+      <c r="B281" s="3" t="inlineStr">
+        <is>
+          <t>mejores lugares para comer botanas cerca del parque ixtepec</t>
+        </is>
+      </c>
+      <c r="C281" s="8" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="D281" s="2" t="inlineStr">
+        <is>
+          <t>0-10</t>
+        </is>
+      </c>
+      <c r="E281" s="2" t="inlineStr">
+        <is>
+          <t>Comparativa</t>
+        </is>
+      </c>
+      <c r="F281" s="3" t="inlineStr">
+        <is>
+          <t>Long-tail alta conversion</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="n">
+        <v>281</v>
+      </c>
+      <c r="B282" s="3" t="inlineStr">
+        <is>
+          <t>mejores lugares para comer botanas de madrugada en el istmo</t>
+        </is>
+      </c>
+      <c r="C282" s="8" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="D282" s="2" t="inlineStr">
+        <is>
+          <t>0-10</t>
+        </is>
+      </c>
+      <c r="E282" s="2" t="inlineStr">
+        <is>
+          <t>Comparativa</t>
+        </is>
+      </c>
+      <c r="F282" s="3" t="inlineStr">
+        <is>
+          <t>Long-tail alta conversion</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="2" t="n">
+        <v>282</v>
+      </c>
+      <c r="B283" s="3" t="inlineStr">
+        <is>
+          <t>precio de alitas picosas de madrugada en el istmo</t>
+        </is>
+      </c>
+      <c r="C283" s="8" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="D283" s="2" t="inlineStr">
+        <is>
+          <t>0-10</t>
+        </is>
+      </c>
+      <c r="E283" s="2" t="inlineStr">
+        <is>
+          <t>Transaccional</t>
+        </is>
+      </c>
+      <c r="F283" s="3" t="inlineStr">
+        <is>
+          <t>Long-tail alta conversion</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="n">
+        <v>283</v>
+      </c>
+      <c r="B284" s="3" t="inlineStr">
+        <is>
+          <t>precio de botanas en el istmo</t>
+        </is>
+      </c>
+      <c r="C284" s="8" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="D284" s="2" t="inlineStr">
+        <is>
+          <t>0-10</t>
+        </is>
+      </c>
+      <c r="E284" s="2" t="inlineStr">
+        <is>
+          <t>Transaccional</t>
+        </is>
+      </c>
+      <c r="F284" s="3" t="inlineStr">
+        <is>
+          <t>Long-tail alta conversion</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="2" t="n">
+        <v>284</v>
+      </c>
+      <c r="B285" s="3" t="inlineStr">
+        <is>
+          <t>precio de comida para llevar cerca del parque ixtepec</t>
+        </is>
+      </c>
+      <c r="C285" s="8" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="D285" s="2" t="inlineStr">
+        <is>
+          <t>0-10</t>
+        </is>
+      </c>
+      <c r="E285" s="2" t="inlineStr">
+        <is>
+          <t>Transaccional</t>
+        </is>
+      </c>
+      <c r="F285" s="3" t="inlineStr">
+        <is>
+          <t>Long-tail alta conversion</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="2" t="n">
+        <v>285</v>
+      </c>
+      <c r="B286" s="3" t="inlineStr">
+        <is>
+          <t>precio de papas a la francesa cerca del parque ixtepec</t>
+        </is>
+      </c>
+      <c r="C286" s="8" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="D286" s="2" t="inlineStr">
+        <is>
+          <t>0-10</t>
+        </is>
+      </c>
+      <c r="E286" s="2" t="inlineStr">
+        <is>
+          <t>Transaccional</t>
+        </is>
+      </c>
+      <c r="F286" s="3" t="inlineStr">
+        <is>
+          <t>Long-tail alta conversion</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="2" t="n">
+        <v>286</v>
+      </c>
+      <c r="B287" s="3" t="inlineStr">
+        <is>
+          <t>precio de papas a la francesa en ciudad ixtepec</t>
+        </is>
+      </c>
+      <c r="C287" s="8" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="D287" s="2" t="inlineStr">
+        <is>
+          <t>0-10</t>
+        </is>
+      </c>
+      <c r="E287" s="2" t="inlineStr">
+        <is>
+          <t>Transaccional</t>
+        </is>
+      </c>
+      <c r="F287" s="3" t="inlineStr">
+        <is>
+          <t>Long-tail alta conversion</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="2" t="n">
+        <v>287</v>
+      </c>
+      <c r="B288" s="3" t="inlineStr">
+        <is>
+          <t>precio de papas a la francesa en el istmo de tehuantepec</t>
+        </is>
+      </c>
+      <c r="C288" s="8" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="D288" s="2" t="inlineStr">
+        <is>
+          <t>0-10</t>
+        </is>
+      </c>
+      <c r="E288" s="2" t="inlineStr">
+        <is>
+          <t>Transaccional</t>
+        </is>
+      </c>
+      <c r="F288" s="3" t="inlineStr">
+        <is>
+          <t>Long-tail alta conversion</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="2" t="n">
+        <v>288</v>
+      </c>
+      <c r="B289" s="3" t="inlineStr">
+        <is>
+          <t>precio de snacks de madrugada en el istmo</t>
+        </is>
+      </c>
+      <c r="C289" s="8" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="D289" s="2" t="inlineStr">
+        <is>
+          <t>0-10</t>
+        </is>
+      </c>
+      <c r="E289" s="2" t="inlineStr">
+        <is>
+          <t>Transaccional</t>
+        </is>
+      </c>
+      <c r="F289" s="3" t="inlineStr">
+        <is>
+          <t>Long-tail alta conversion</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="2" t="n">
+        <v>289</v>
+      </c>
+      <c r="B290" s="3" t="inlineStr">
+        <is>
           <t>precio de snacks en ciudad ixtepec</t>
         </is>
       </c>
-      <c r="C243" s="8" t="inlineStr">
+      <c r="C290" s="8" t="inlineStr">
         <is>
           <t>BAJO</t>
         </is>
       </c>
-      <c r="D243" s="2" t="inlineStr">
+      <c r="D290" s="2" t="inlineStr">
         <is>
           <t>0-10</t>
         </is>
       </c>
-      <c r="E243" s="2" t="inlineStr">
+      <c r="E290" s="2" t="inlineStr">
         <is>
           <t>Transaccional</t>
         </is>
       </c>
-      <c r="F243" s="3" t="inlineStr">
+      <c r="F290" s="3" t="inlineStr">
         <is>
           <t>Long-tail alta conversion</t>
         </is>
